--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -954,10 +954,8 @@
           <t>INDIRA RANABHAT</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9866471440</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9866471440</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -972,10 +970,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9860365129</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9860365129</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -992,10 +988,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.665254</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.665254</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1047,25 +1041,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>L1-1</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.374492</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.374492</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
@@ -1114,7 +1104,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1434,7 +1424,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW3"/>
+  <dimension ref="A1:AW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,12 +496,12 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -511,25 +511,25 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="10" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -1084,6 +1084,432 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 9:14 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334736</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Dipendra Shrestha</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Dipendra Shrestha</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9765920115</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:14:43 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9765920115</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:19:43 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:14:43 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.650029</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Mahalaxmi 44700 near by Shikhar School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>9765920115@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>04:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Magar</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>2,6</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.34511</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>17h 55m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 9:07 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335101</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Shrestha</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Shrestha</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9841230897</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:07:15 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9849942358</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:31:59 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:07:15 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.70218</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Mulpani , Thapagaun , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>shresthasudip3891@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Anusha Adhikari</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L55-7</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.38441</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>12h 35m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1095,16 +1521,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1132,7 +1558,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1142,7 +1568,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1153,7 +1579,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1603,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>15h 2m</t>
+          <t>15h 10m</t>
         </is>
       </c>
     </row>
@@ -1230,231 +1656,447 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr"/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
       <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr"/>
-      <c r="B16" s="3" t="inlineStr"/>
-      <c r="C16" s="3" t="n">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>TKT1334942</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>INDIRA RANABHAT</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>16 Sep 2026 08:35:54 AM</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 05:33:53 PM</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>16 Sep 2026 08:35:54 AM</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t>15h 2m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334736</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Dipendra Shrestha</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:14:43 AM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:19:43 PM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:14:43 AM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>17h 55m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335101</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Shrestha</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:07:15 AM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:31:59 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:07:15 AM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>12h 35m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
@@ -532,7 +532,7 @@
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="28" customWidth="1" min="47" max="47"/>
+    <col width="32" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -1151,10 +1151,8 @@
           <t>Dipendra Shrestha</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9765920115</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9765920115</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1169,10 +1167,8 @@
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>9765920115</t>
-        </is>
+      <c r="U4" s="3" t="n">
+        <v>9765920115</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1189,10 +1185,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.650029</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.650029</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1230,10 +1224,8 @@
           <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
-      <c r="AH4" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH4" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI4" s="3" t="inlineStr">
         <is>
@@ -1252,25 +1244,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>2,6</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.34511</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.34511000000001</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1366,10 +1354,8 @@
           <t>Sudip Shrestha</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9841230897</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9841230897</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1384,10 +1370,8 @@
       </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>9849942358</t>
-        </is>
+      <c r="U5" s="3" t="n">
+        <v>9849942358</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1404,10 +1388,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.70218</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.70218</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1463,50 +1445,253 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L55-7</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.38441</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.38441</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>12h 35m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
           <t>Case : iptv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t>12h 35m</t>
-        </is>
-      </c>
-      <c r="AU5" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV5" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 9:20 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Router faulty</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335310</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Rojan Khadka</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Rojan Khadka</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9841027827</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:02:41 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9841027827</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:01:52 AM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:20:17 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.6636</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Imadol-1,Lalitpur,near Imadol Krishna mandir,, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>rojankhadka76@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>CDB324</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.34176</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>17m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>18m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1530,7 +1715,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1558,7 +1743,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1579,7 +1764,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -1662,14 +1847,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1789,202 +1974,158 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="3" t="inlineStr"/>
-      <c r="C20" s="3" t="n">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1334942</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>INDIRA RANABHAT</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 08:35:54 AM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 05:33:53 PM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 08:35:54 AM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>15h 2m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1334736</t>
+          <t>TKT1334942</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Dipendra Shrestha</t>
+          <t>INDIRA RANABHAT</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -1999,27 +2140,27 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:14:43 AM</t>
+          <t>16 Sep 2026 08:35:54 AM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:19:43 PM</t>
+          <t>15 Sep 2026 05:33:53 PM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:14:43 AM</t>
+          <t>16 Sep 2026 08:35:54 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -2029,72 +2170,139 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>17h 55m</t>
+          <t>15h 2m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>TKT1334736</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Dipendra Shrestha</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:14:43 AM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:19:43 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:14:43 AM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>17h 55m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>TKT1335101</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Sudip Shrestha</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Case : iptv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>16 Sep 2026 09:07:15 AM</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>15 Sep 2026 08:31:59 PM</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>16 Sep 2026 09:07:15 AM</t>
         </is>
       </c>
-      <c r="L26" s="3" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>12h 35m</t>
         </is>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1555,10 +1555,8 @@
           <t>Rojan Khadka</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9841027827</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9841027827</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1573,10 +1571,8 @@
       </c>
       <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="inlineStr"/>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>9841027827</t>
-        </is>
+      <c r="U6" s="3" t="n">
+        <v>9841027827</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1593,10 +1589,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.6636</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.6636</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1648,50 +1642,257 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>CDB324</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.34176</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.34175999999999</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>17m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>18m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
           <t>Case : Router faulty   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS6" s="3" t="inlineStr">
-        <is>
-          <t>17m</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>18m</t>
-        </is>
-      </c>
-      <c r="AU6" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV6" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router faulty   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW6" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 9:44 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335000</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Saman Shrestha</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Saman Shrestha</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9860694555</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:44:13 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9860694555</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:47:39 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:44:13 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.72319</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Near JENISHA TEA SHOP, Boudha Rd, Gokarneshwor, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>samanshresthaaa@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>01:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>L25-7</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.3798</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>14h 56m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1715,7 +1916,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1743,7 +1944,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1753,7 +1954,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1764,7 +1965,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1989,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>15h 10m</t>
+          <t>15h 7m</t>
         </is>
       </c>
     </row>
@@ -1829,10 +2030,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -1937,10 +2138,10 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -2308,6 +2509,73 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335000</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Saman Shrestha</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:44:13 AM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:47:39 PM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:44:13 AM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>14h 56m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1752,10 +1752,8 @@
           <t>Saman Shrestha</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9860694555</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9860694555</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1770,10 +1768,8 @@
       </c>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>9860694555</t>
-        </is>
+      <c r="U7" s="3" t="n">
+        <v>9860694555</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1790,10 +1786,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.72319</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.72319</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1849,25 +1843,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>L25-7</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.3798</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.3798</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -1916,7 +1906,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2542,7 +2532,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,11 +483,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -506,11 +506,11 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -527,9 +527,9 @@
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1886,6 +1886,619 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:03 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334960</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Raju Tamang</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Raju Tamang</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9828136234</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:03:37 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9818268813</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:50:27 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:03:37 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Bhagwati Temple - Hindu temple P9QM+6W3 Gokarneshwor 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>rajut4465@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>02:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L48-2</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>16h 13m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:13 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334766</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>prakash thimi</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>prakash thimi</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9843350962</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:02:44 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>BKT9843350962</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:38:44 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:13:19 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>sallaghari, Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>9843350962@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L24-1</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>12h 10m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>18h 34m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:06 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>slow internet issue</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334610</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>kran nepali</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>kran nepali</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9865129512</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:06:51 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>BKT9865129512</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:58:57 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:06:51 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.709873453420194</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>suryabanyak , Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>abcde@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>06:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Namuna Acharya</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>L27-4</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.3187942504883</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>20h 7m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1897,7 +2510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1906,7 +2519,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1934,7 +2547,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -1944,7 +2557,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -1979,7 +2592,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>15h 7m</t>
+          <t>16h 8m</t>
         </is>
       </c>
     </row>
@@ -2020,10 +2633,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -2056,14 +2669,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2128,10 +2741,10 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -2142,12 +2755,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -2170,287 +2783,199 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr"/>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="n">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1334942</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>INDIRA RANABHAT</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 08:35:54 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 05:33:53 PM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 08:35:54 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>15h 2m</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1334736</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Dipendra Shrestha</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>NETTV-No internet connection in STB</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 09:14:43 AM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 03:19:43 PM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 09:14:43 AM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>17h 55m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1335101</t>
+          <t>TKT1334942</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Sudip Shrestha</t>
+          <t>INDIRA RANABHAT</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -2470,22 +2995,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:07:15 AM</t>
+          <t>16 Sep 2026 08:35:54 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:31:59 PM</t>
+          <t>15 Sep 2026 05:33:53 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:07:15 AM</t>
+          <t>16 Sep 2026 08:35:54 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -2495,74 +3020,342 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>12h 35m</t>
+          <t>15h 2m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
+          <t>TKT1334736</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Dipendra Shrestha</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:14:43 AM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:19:43 PM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:14:43 AM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>17h 55m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1335101</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Sudip Shrestha</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:07:15 AM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:31:59 PM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:07:15 AM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>12h 35m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
           <t>TKT1335000</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Saman Shrestha</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>16 Sep 2026 09:44:13 AM</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 06:47:39 PM</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>16 Sep 2026 09:44:13 AM</t>
         </is>
       </c>
-      <c r="L28" s="3" t="inlineStr">
+      <c r="L30" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr">
+      <c r="M30" s="3" t="inlineStr">
         <is>
           <t>14h 56m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334960</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Raju Tamang</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:03:37 AM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:50:27 PM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:03:37 AM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>16h 13m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334610</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>kran nepali</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:06:51 AM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:58:57 PM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:06:51 AM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>20h 7m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW10"/>
+  <dimension ref="A1:AW14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -510,12 +510,12 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="21" customWidth="1" min="25" max="25"/>
+    <col width="19" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="30" customWidth="1" min="32" max="32"/>
     <col width="38" customWidth="1" min="33" max="33"/>
@@ -523,7 +523,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="21" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -1953,10 +1953,8 @@
           <t>Raju Tamang</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9828136234</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9828136234</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2046,10 +2044,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
@@ -2060,7 +2056,7 @@
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2146,20 +2142,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr">
         <is>
           <t>prakash thimi</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9843350962</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9843350962</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2245,10 +2235,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2259,7 +2247,7 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2355,10 +2343,8 @@
           <t>kran nepali</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9865129512</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9865129512</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2393,10 +2379,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.709873453420194</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.7098734534202</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2452,48 +2436,876 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>L27-4</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.3187942504883</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.3187942504883</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>20h 7m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
           <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS10" s="3" t="inlineStr">
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:18 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335114</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Bishnu Bikram Khatri</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Bishnu Bikram Khatri</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9810318569</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:18:36 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9886582995</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:43:35 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:18:36 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.729</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Near Cake Palace, Jorpati Sundarijal road, Jorpati- 8, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>bishnukhatri283@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>00:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L1-1</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.3788</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT10" s="3" t="inlineStr">
-        <is>
-          <t>20h 7m</t>
-        </is>
-      </c>
-      <c r="AU10" s="3" t="inlineStr">
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>13h 35m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV10" s="3" t="inlineStr">
-        <is>
-          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW10" s="3" t="inlineStr">
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:29 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>A46UWsNL7J/c+OCnFBgFhw==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1191679</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Gagan Kafle</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Gagan Kafle</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9851351392</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>15 Jun 2026 03:38:40 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9861590282</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>24 May 2026 02:53:39 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:29:56 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.7057</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Near Kumari Bank Limited - Bank P849+9M8 Bag Bazar Sadak Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>gagan.kafle5@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>20:29 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Shristi Shrestha</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>4,5</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.319426</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>92d 18h 51m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>114d 19h 36m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:29 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>A46UWsNL7J/c+OCnFBgFhw==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1207844</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Phursona Sherpa</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Phursona Sherpa</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9849436647</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>13 Jun 2026 01:15:04 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>CHB9849436647</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>06 Jun 2026 02:40:21 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:29:30 AM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Near By Kapan Aakase Dhara - Drinking water, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>01:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Govinda Chaulagain</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>L18-4</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>94d 21h 14m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>101d 19h 49m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:26 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>A46UWsNL7J/c+OCnFBgFhw==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : Set up box not working   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Set up box not working</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1209820</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Sanjib Thapa Magar</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Sanjib Thapa Magar</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9803736348</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>13 Jun 2026 01:46:51 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9803736348</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>07 Jun 2026 09:07:12 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:26:14 AM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.719152</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Near Nepal Telecom,P9CG+92R, ??????? ???, Gokarneshwor 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>tsanjeev08@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>20:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Om Neupane</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>L51-5</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.374791</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : Set up box not working   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>94d 20h 39m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>100d 13h 19m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : Set up box not working   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -2510,7 +3322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2547,7 +3359,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -2557,7 +3369,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -2568,7 +3380,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -2580,7 +3392,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>28d 6h 4m</t>
         </is>
       </c>
     </row>
@@ -2592,7 +3404,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>16h 8m</t>
+          <t>32d 4h 18m</t>
         </is>
       </c>
     </row>
@@ -2633,10 +3445,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -2651,14 +3463,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2741,10 +3553,10 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -2783,7 +3595,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -2806,41 +3618,41 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2852,197 +3664,153 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
       <c r="C23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TKT1334942</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>INDIRA RANABHAT</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 08:35:54 AM</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 05:33:53 PM</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 08:35:54 AM</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>15h 2m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1334736</t>
+          <t>TKT1334942</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Dipendra Shrestha</t>
+          <t>INDIRA RANABHAT</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -3062,22 +3830,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:14:43 AM</t>
+          <t>16 Sep 2026 08:35:54 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:19:43 PM</t>
+          <t>15 Sep 2026 05:33:53 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:14:43 AM</t>
+          <t>16 Sep 2026 08:35:54 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -3087,29 +3855,29 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>17h 55m</t>
+          <t>15h 2m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1335101</t>
+          <t>TKT1334736</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Sudip Shrestha</t>
+          <t>Dipendra Shrestha</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3129,22 +3897,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:07:15 AM</t>
+          <t>16 Sep 2026 09:14:43 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:31:59 PM</t>
+          <t>15 Sep 2026 03:19:43 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:07:15 AM</t>
+          <t>16 Sep 2026 09:14:43 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -3154,29 +3922,29 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>12h 35m</t>
+          <t>17h 55m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1335000</t>
+          <t>TKT1335101</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Saman Shrestha</t>
+          <t>Sudip Shrestha</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -3196,22 +3964,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:44:13 AM</t>
+          <t>16 Sep 2026 09:07:15 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 06:47:39 PM</t>
+          <t>15 Sep 2026 08:31:59 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:44:13 AM</t>
+          <t>16 Sep 2026 09:07:15 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -3221,19 +3989,19 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>14h 56m</t>
+          <t>12h 35m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1334960</t>
+          <t>TKT1335000</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Raju Tamang</t>
+          <t>Saman Shrestha</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -3258,27 +4026,27 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:03:37 AM</t>
+          <t>16 Sep 2026 09:44:13 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:50:27 PM</t>
+          <t>15 Sep 2026 06:47:39 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:03:37 AM</t>
+          <t>16 Sep 2026 09:44:13 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -3288,74 +4056,409 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>16h 13m</t>
+          <t>14h 56m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
+          <t>TKT1334960</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Raju Tamang</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:03:37 AM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:50:27 PM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:03:37 AM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>16h 13m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
           <t>TKT1334610</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>kran nepali</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade Dual Band</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>16 Sep 2026 10:06:51 AM</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>15 Sep 2026 01:58:57 PM</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>16 Sep 2026 10:06:51 AM</t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr">
         <is>
           <t>20h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335114</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Bishnu Bikram Khatri</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:18:36 AM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:43:35 PM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:18:36 AM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>13h 35m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1191679</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Gagan Kafle</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>15 Jun 2026 03:38:40 PM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>24 May 2026 02:53:39 PM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:29:56 AM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>92d 18h 51m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>114d 19h 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1207844</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Phursona Sherpa</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>13 Jun 2026 01:15:04 PM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>06 Jun 2026 02:40:21 PM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:29:30 AM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>94d 21h 14m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>101d 19h 49m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1209820</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Sanjib Thapa Magar</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : Set up box not working   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : Set up box not working   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>13 Jun 2026 01:46:51 PM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>07 Jun 2026 09:07:12 PM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:26:14 AM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>94d 20h 39m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>100d 13h 19m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW14"/>
+  <dimension ref="A1:AW21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="11" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="34" customWidth="1" min="32" max="32"/>
     <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -2546,10 +2546,8 @@
           <t>Bishnu Bikram Khatri</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9810318569</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9810318569</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2584,10 +2582,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.729</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.729</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -2643,25 +2639,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>L1-1</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.3788</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.3788</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -2753,10 +2745,8 @@
           <t>Gagan Kafle</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9851351392</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9851351392</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2791,10 +2781,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.7057</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.7057</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -2850,25 +2838,21 @@
           <t>Om Neupane</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>4,5</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.319426</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.31942600000001</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Om Neupane</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -2964,10 +2948,8 @@
           <t>Phursona Sherpa</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9849436647</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9849436647</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3057,10 +3039,8 @@
           <t>Om Neupane</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
@@ -3071,7 +3051,7 @@
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Om Neupane</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3167,10 +3147,8 @@
           <t>Sanjib Thapa Magar</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9803736348</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9803736348</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3205,10 +3183,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.719152</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.719152</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3264,48 +3240,1493 @@
           <t>Om Neupane</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>L51-5</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.374791</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.374791</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>94d 20h 39m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>100d 13h 19m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
           <t>Case : Set up box not working   has been updated by Om Neupane</t>
         </is>
       </c>
-      <c r="AS14" s="3" t="inlineStr">
-        <is>
-          <t>94d 20h 39m</t>
-        </is>
-      </c>
-      <c r="AT14" s="3" t="inlineStr">
-        <is>
-          <t>100d 13h 19m</t>
-        </is>
-      </c>
-      <c r="AU14" s="3" t="inlineStr">
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:37 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>wifi6 router</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334895</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>DITSA TECHNOLOGY PVT. LTD</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>DITSA TECHNOLOGY PVT. LTD</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9867676078</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:37:31 AM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9867676078</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:04:24 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:37:31 AM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>gatthaghar orbit school, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>ditsadigitalmarketing@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>03:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Laxmi Karki</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>L26-5</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>17h 33m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV14" s="3" t="inlineStr">
-        <is>
-          <t>Case : Set up box not working   has been updated by Om Neupane</t>
-        </is>
-      </c>
-      <c r="AW14" s="3" t="inlineStr">
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:45 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335451</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Kushang Shrepa</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Kushang Shrepa</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9843545310</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:27:52 AM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9843545310</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:27:52 AM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:45:32 AM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Kapan,kharibot ani gumba Details from Google Maps P9Q7+2P3, Kapan Marg, Kathmandu 44600, Bagmati, Ce</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>sbawa5622@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>L37-6</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>17m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>17m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:43 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : single to dual  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>single to dual</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334694</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Raj Kumar Thapa</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Raj Kumar Thapa</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9851160619</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:45:17 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9851160619</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:45:17 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:43:02 AM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.71607</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Sarbeshwor Mahadev Temple,Kathmandu , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>rkthapa99@yahoo.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.36851</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : single to dual  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>19h 57m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>19h 57m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : single to dual  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:35 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334982</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Rinji Sherpa</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Rinji Sherpa</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9863841961</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:35:51 AM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9863841961</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:26:14 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:35:51 AM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.73566</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Aarubari Chowk,Green Tara Child Heaven School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr"/>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>02:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>L39-8</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.3775</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>16h 9m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:43 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>slow internet</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334412</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Kishwor Khanal</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Kishwor Khanal</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9843123637</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:22:53 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9843123637</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:00:05 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:43:20 AM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.705894</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Purnima Press Details from Google Maps P844+M85, Sahid Nigurna Marg, Kathmandu 44600, Bagmati, Centr</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>CDB288</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.306163</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>18h 20m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>22h 43m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:27 AM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>5  g   not shown</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334968</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Pramod Pandey</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Pramod Pandey</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9844376935</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:27:53 AM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9844376935</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:00:47 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:27:53 AM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.68895</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Kritipur ward no:2,Maitrinagar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>prakriteepandey@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>02:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Bashu Bhat</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>4,15</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.27805</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>16h 27m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:22 AM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>5  g   not shown</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334968</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Pramod Pandey</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Pramod Pandey</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9844376935</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:27:53 AM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9844376935</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:00:47 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:27:53 AM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.68895</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Kritipur ward no:2,Maitrinagar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>prakriteepandey@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>02:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Bashu Bhat</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>4,15</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.27805</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>16h 27m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -3322,7 +4743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3359,7 +4780,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -3369,7 +4790,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -3380,7 +4801,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -3392,7 +4813,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>28d 6h 4m</t>
+          <t>20d 4h 20m</t>
         </is>
       </c>
     </row>
@@ -3404,7 +4825,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>32d 4h 18m</t>
+          <t>23d 4h 24m</t>
         </is>
       </c>
     </row>
@@ -3445,14 +4866,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -3481,86 +4902,81 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
       <c r="B13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
@@ -3572,41 +4988,41 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3618,7 +5034,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -3641,41 +5057,41 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3687,264 +5103,176 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr"/>
-      <c r="B24" s="3" t="inlineStr"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
       <c r="C24" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>TKT1334942</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>INDIRA RANABHAT</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 08:35:54 AM</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 05:33:53 PM</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 08:35:54 AM</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>15h 2m</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>TKT1334736</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Dipendra Shrestha</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>NETTV-No internet connection in STB</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 09:14:43 AM</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 03:19:43 PM</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 09:14:43 AM</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>17h 55m</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1335101</t>
+          <t>TKT1334942</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Sudip Shrestha</t>
+          <t>INDIRA RANABHAT</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -3964,22 +5292,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:07:15 AM</t>
+          <t>16 Sep 2026 08:35:54 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:31:59 PM</t>
+          <t>15 Sep 2026 05:33:53 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:07:15 AM</t>
+          <t>16 Sep 2026 08:35:54 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -3989,29 +5317,29 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>12h 35m</t>
+          <t>15h 2m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1335000</t>
+          <t>TKT1334736</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Saman Shrestha</t>
+          <t>Dipendra Shrestha</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -4031,22 +5359,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:44:13 AM</t>
+          <t>16 Sep 2026 09:14:43 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 06:47:39 PM</t>
+          <t>15 Sep 2026 03:19:43 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:44:13 AM</t>
+          <t>16 Sep 2026 09:14:43 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -4056,29 +5384,29 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>14h 56m</t>
+          <t>17h 55m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1334960</t>
+          <t>TKT1335101</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Raju Tamang</t>
+          <t>Sudip Shrestha</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4098,22 +5426,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:03:37 AM</t>
+          <t>16 Sep 2026 09:07:15 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:50:27 PM</t>
+          <t>15 Sep 2026 08:31:59 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:03:37 AM</t>
+          <t>16 Sep 2026 09:07:15 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -4123,19 +5451,19 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>16h 13m</t>
+          <t>12h 35m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1334610</t>
+          <t>TKT1335000</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>kran nepali</t>
+          <t>Saman Shrestha</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -4145,7 +5473,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -4165,22 +5493,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:06:51 AM</t>
+          <t>16 Sep 2026 09:44:13 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:58:57 PM</t>
+          <t>15 Sep 2026 06:47:39 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:06:51 AM</t>
+          <t>16 Sep 2026 09:44:13 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -4190,19 +5518,19 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>20h 7m</t>
+          <t>14h 56m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1335114</t>
+          <t>TKT1334960</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Bishnu Bikram Khatri</t>
+          <t>Raju Tamang</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -4227,27 +5555,27 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:18:36 AM</t>
+          <t>16 Sep 2026 10:03:37 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:43:35 PM</t>
+          <t>15 Sep 2026 05:50:27 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:18:36 AM</t>
+          <t>16 Sep 2026 10:03:37 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -4257,19 +5585,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>13h 35m</t>
+          <t>16h 13m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1191679</t>
+          <t>TKT1334610</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Gagan Kafle</t>
+          <t>kran nepali</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -4279,7 +5607,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -4294,49 +5622,49 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Om Neupane</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Om Neupane</t>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>15 Jun 2026 03:38:40 PM</t>
+          <t>16 Sep 2026 10:06:51 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>24 May 2026 02:53:39 PM</t>
+          <t>15 Sep 2026 01:58:57 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:29:56 AM</t>
+          <t>16 Sep 2026 10:06:51 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>92d 18h 51m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>114d 19h 36m</t>
+          <t>20h 7m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1207844</t>
+          <t>TKT1335114</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Phursona Sherpa</t>
+          <t>Bishnu Bikram Khatri</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -4361,104 +5689,506 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Om Neupane</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Om Neupane</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>13 Jun 2026 01:15:04 PM</t>
+          <t>16 Sep 2026 10:18:36 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>06 Jun 2026 02:40:21 PM</t>
+          <t>15 Sep 2026 08:43:35 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:29:30 AM</t>
+          <t>16 Sep 2026 10:18:36 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>94d 21h 14m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>101d 19h 49m</t>
+          <t>13h 35m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
+          <t>TKT1191679</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Gagan Kafle</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>15 Jun 2026 03:38:40 PM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>24 May 2026 02:53:39 PM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:29:56 AM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>92d 18h 51m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>114d 19h 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1207844</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Phursona Sherpa</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Om Neupane</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>13 Jun 2026 01:15:04 PM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>06 Jun 2026 02:40:21 PM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:29:30 AM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>94d 21h 14m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>101d 19h 49m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
           <t>TKT1209820</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Sanjib Thapa Magar</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>Case : Set up box not working   has been updated by Om Neupane</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>Case : Set up box not working   has been updated by Om Neupane</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>13 Jun 2026 01:46:51 PM</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>07 Jun 2026 09:07:12 PM</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>16 Sep 2026 10:26:14 AM</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>94d 20h 39m</t>
         </is>
       </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr">
         <is>
           <t>100d 13h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334895</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>DITSA TECHNOLOGY PVT. LTD</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:37:31 AM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:04:24 PM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:37:31 AM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>17h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334982</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Rinji Sherpa</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:35:51 AM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:26:14 PM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:35:51 AM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>16h 9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334968</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Pramod Pandey</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:27:53 AM</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:00:47 PM</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:27:53 AM</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>16h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334968</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Pramod Pandey</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:27:53 AM</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:00:47 PM</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:27:53 AM</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>16h 27m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW21"/>
+  <dimension ref="A1:AW22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3350,10 +3350,8 @@
           <t>DITSA TECHNOLOGY PVT. LTD</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9867676078</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9867676078</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3443,10 +3441,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
@@ -3457,7 +3453,7 @@
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6 router  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -3553,10 +3549,8 @@
           <t>Kushang Shrepa</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9843545310</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9843545310</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3591,10 +3585,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -3646,25 +3638,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>L37-6</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -3760,10 +3748,8 @@
           <t>Raj Kumar Thapa</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9851160619</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9851160619</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3798,10 +3784,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.71607</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.71607</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -3853,25 +3837,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.36851</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.36851</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : single to dual  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -3967,10 +3947,8 @@
           <t>Rinji Sherpa</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9863841961</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9863841961</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4005,10 +3983,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.73566</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.73566</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -4060,25 +4036,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>L39-8</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.3775</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.3775</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4174,10 +4146,8 @@
           <t>Kishwor Khanal</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9843123637</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9843123637</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4212,10 +4182,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>27.705894</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>27.705894</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -4263,25 +4231,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>CDB288</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.306163</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.306163</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -4377,10 +4341,8 @@
           <t>Pramod Pandey</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9844376935</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9844376935</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4415,10 +4377,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>27.68895</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>27.68895</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -4474,25 +4434,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>4,15</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.27805</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.27804999999999</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -4588,10 +4544,8 @@
           <t>Pramod Pandey</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9844376935</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9844376935</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4626,10 +4580,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>27.68895</t>
-        </is>
+      <c r="Y21" s="3" t="n">
+        <v>27.68895</v>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -4685,48 +4637,147 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>4,15</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.27805</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.27804999999999</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>16h 27m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
           <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS21" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT21" s="3" t="inlineStr">
-        <is>
-          <t>16h 27m</t>
-        </is>
-      </c>
-      <c r="AU21" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV21" s="3" t="inlineStr">
-        <is>
-          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:50 AM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light in router   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="inlineStr"/>
+      <c r="O22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr"/>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr"/>
+      <c r="V22" s="3" t="inlineStr"/>
+      <c r="W22" s="3" t="inlineStr"/>
+      <c r="X22" s="3" t="inlineStr"/>
+      <c r="Y22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="inlineStr"/>
+      <c r="AA22" s="3" t="inlineStr"/>
+      <c r="AB22" s="3" t="inlineStr"/>
+      <c r="AC22" s="3" t="inlineStr"/>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr"/>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr"/>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr"/>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr"/>
+      <c r="AM22" s="3" t="inlineStr"/>
+      <c r="AN22" s="3" t="inlineStr"/>
+      <c r="AO22" s="3" t="inlineStr"/>
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light in router   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -4752,7 +4803,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4780,7 +4831,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -4801,7 +4852,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -5957,7 +6008,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6 router  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -6024,7 +6075,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -6091,7 +6142,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -6158,7 +6209,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW22"/>
+  <dimension ref="A1:AW26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4783,6 +4783,418 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:03 AM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr"/>
+      <c r="O23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr"/>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr"/>
+      <c r="V23" s="3" t="inlineStr"/>
+      <c r="W23" s="3" t="inlineStr"/>
+      <c r="X23" s="3" t="inlineStr"/>
+      <c r="Y23" s="3" t="inlineStr"/>
+      <c r="Z23" s="3" t="inlineStr"/>
+      <c r="AA23" s="3" t="inlineStr"/>
+      <c r="AB23" s="3" t="inlineStr"/>
+      <c r="AC23" s="3" t="inlineStr"/>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr"/>
+      <c r="AF23" s="3" t="inlineStr"/>
+      <c r="AG23" s="3" t="inlineStr"/>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr"/>
+      <c r="AM23" s="3" t="inlineStr"/>
+      <c r="AN23" s="3" t="inlineStr"/>
+      <c r="AO23" s="3" t="inlineStr"/>
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:02 AM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr"/>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr"/>
+      <c r="V24" s="3" t="inlineStr"/>
+      <c r="W24" s="3" t="inlineStr"/>
+      <c r="X24" s="3" t="inlineStr"/>
+      <c r="Y24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="inlineStr"/>
+      <c r="AA24" s="3" t="inlineStr"/>
+      <c r="AB24" s="3" t="inlineStr"/>
+      <c r="AC24" s="3" t="inlineStr"/>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr"/>
+      <c r="AF24" s="3" t="inlineStr"/>
+      <c r="AG24" s="3" t="inlineStr"/>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr"/>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr"/>
+      <c r="AM24" s="3" t="inlineStr"/>
+      <c r="AN24" s="3" t="inlineStr"/>
+      <c r="AO24" s="3" t="inlineStr"/>
+      <c r="AP24" s="3" t="inlineStr"/>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:13 AM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr"/>
+      <c r="O25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr"/>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr"/>
+      <c r="V25" s="3" t="inlineStr"/>
+      <c r="W25" s="3" t="inlineStr"/>
+      <c r="X25" s="3" t="inlineStr"/>
+      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Z25" s="3" t="inlineStr"/>
+      <c r="AA25" s="3" t="inlineStr"/>
+      <c r="AB25" s="3" t="inlineStr"/>
+      <c r="AC25" s="3" t="inlineStr"/>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr"/>
+      <c r="AF25" s="3" t="inlineStr"/>
+      <c r="AG25" s="3" t="inlineStr"/>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr"/>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr"/>
+      <c r="AM25" s="3" t="inlineStr"/>
+      <c r="AN25" s="3" t="inlineStr"/>
+      <c r="AO25" s="3" t="inlineStr"/>
+      <c r="AP25" s="3" t="inlineStr"/>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:02 AM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="inlineStr"/>
+      <c r="O26" s="3" t="inlineStr"/>
+      <c r="P26" s="3" t="inlineStr"/>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr"/>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr"/>
+      <c r="V26" s="3" t="inlineStr"/>
+      <c r="W26" s="3" t="inlineStr"/>
+      <c r="X26" s="3" t="inlineStr"/>
+      <c r="Y26" s="3" t="inlineStr"/>
+      <c r="Z26" s="3" t="inlineStr"/>
+      <c r="AA26" s="3" t="inlineStr"/>
+      <c r="AB26" s="3" t="inlineStr"/>
+      <c r="AC26" s="3" t="inlineStr"/>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr"/>
+      <c r="AF26" s="3" t="inlineStr"/>
+      <c r="AG26" s="3" t="inlineStr"/>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr"/>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr"/>
+      <c r="AM26" s="3" t="inlineStr"/>
+      <c r="AN26" s="3" t="inlineStr"/>
+      <c r="AO26" s="3" t="inlineStr"/>
+      <c r="AP26" s="3" t="inlineStr"/>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4831,7 +5243,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -4852,7 +5264,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>56.0%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW26"/>
+  <dimension ref="A1:AW29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -497,7 +497,7 @@
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="28" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -521,7 +521,7 @@
     <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="26" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="21" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
@@ -529,10 +529,10 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -5195,6 +5195,647 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:47 AM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334824</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Babu Ram Sunwar</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Babu Ram Sunwar</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9803861981</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:13:19 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9803861981</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:13:19 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:47:17 AM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.695218</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Near Mangalodaya Multiple CampusM6V8+R29, Chandragiri 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr"/>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>05:34 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>CDB154</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.219987</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>19h 33m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>19h 33m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:41 AM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333669</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Shankar Barahi</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Shankar Barahi</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9841285814</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:41:03 AM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>9841285814</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:35:12 PM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:41:03 AM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>27.657276</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>Sangam Dairy, Imadole , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>barahiprerak@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>16:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>1,9</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>85.341635</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 5m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:36 AM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Router faulty</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335310</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Rojan Khadka</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Rojan Khadka</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9841027827</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:44:02 AM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 01: 01:00 PM</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9841027827</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:01:52 AM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:44:02 AM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>27.6636</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>Hari Rijal</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Imadol-1,Lalitpur,near Imadol Krishna mandir,, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>rojankhadka76@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>01:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr">
+        <is>
+          <t>22:25 hour / 00:00 hour</t>
+        </is>
+      </c>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>CDB324</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>85.34176</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>2h 42m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5206,7 +5847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5215,7 +5856,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5243,7 +5884,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -5253,7 +5894,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -5264,7 +5905,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5917,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>20d 4h 20m</t>
+          <t>17d 17h 1m</t>
         </is>
       </c>
     </row>
@@ -5288,7 +5929,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>23d 4h 24m</t>
+          <t>20d 10h 50m</t>
         </is>
       </c>
     </row>
@@ -5329,14 +5970,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>84.6%</t>
         </is>
       </c>
     </row>
@@ -5383,14 +6024,14 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -5455,14 +6096,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
@@ -5628,181 +6269,137 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr"/>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
       <c r="C26" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>TKT1334942</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>INDIRA RANABHAT</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 08:35:54 AM</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 05:33:53 PM</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 08:35:54 AM</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>15h 2m</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1334736</t>
+          <t>TKT1334942</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Dipendra Shrestha</t>
+          <t>INDIRA RANABHAT</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -5822,22 +6419,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:14:43 AM</t>
+          <t>16 Sep 2026 08:35:54 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:19:43 PM</t>
+          <t>15 Sep 2026 05:33:53 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:14:43 AM</t>
+          <t>16 Sep 2026 08:35:54 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -5847,29 +6444,29 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>17h 55m</t>
+          <t>15h 2m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1335101</t>
+          <t>TKT1334736</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Sudip Shrestha</t>
+          <t>Dipendra Shrestha</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -5889,22 +6486,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:07:15 AM</t>
+          <t>16 Sep 2026 09:14:43 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:31:59 PM</t>
+          <t>15 Sep 2026 03:19:43 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:07:15 AM</t>
+          <t>16 Sep 2026 09:14:43 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -5914,29 +6511,29 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>12h 35m</t>
+          <t>17h 55m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1335000</t>
+          <t>TKT1335101</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Saman Shrestha</t>
+          <t>Sudip Shrestha</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -5956,22 +6553,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:44:13 AM</t>
+          <t>16 Sep 2026 09:07:15 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 06:47:39 PM</t>
+          <t>15 Sep 2026 08:31:59 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:44:13 AM</t>
+          <t>16 Sep 2026 09:07:15 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -5981,19 +6578,19 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>14h 56m</t>
+          <t>12h 35m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1334960</t>
+          <t>TKT1335000</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Raju Tamang</t>
+          <t>Saman Shrestha</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -6028,17 +6625,17 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:03:37 AM</t>
+          <t>16 Sep 2026 09:44:13 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:50:27 PM</t>
+          <t>15 Sep 2026 06:47:39 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:03:37 AM</t>
+          <t>16 Sep 2026 09:44:13 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -6048,19 +6645,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>16h 13m</t>
+          <t>14h 56m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1334610</t>
+          <t>TKT1334960</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>kran nepali</t>
+          <t>Raju Tamang</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -6070,7 +6667,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -6090,22 +6687,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:06:51 AM</t>
+          <t>16 Sep 2026 10:03:37 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:58:57 PM</t>
+          <t>15 Sep 2026 05:50:27 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:06:51 AM</t>
+          <t>16 Sep 2026 10:03:37 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -6115,19 +6712,19 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>20h 7m</t>
+          <t>16h 13m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1335114</t>
+          <t>TKT1334610</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Bishnu Bikram Khatri</t>
+          <t>kran nepali</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -6137,7 +6734,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -6157,22 +6754,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:18:36 AM</t>
+          <t>16 Sep 2026 10:06:51 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:43:35 PM</t>
+          <t>15 Sep 2026 01:58:57 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:18:36 AM</t>
+          <t>16 Sep 2026 10:06:51 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -6182,19 +6779,19 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>13h 35m</t>
+          <t>20h 7m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1191679</t>
+          <t>TKT1335114</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Gagan Kafle</t>
+          <t>Bishnu Bikram Khatri</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -6224,44 +6821,44 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Om Neupane</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>15 Jun 2026 03:38:40 PM</t>
+          <t>16 Sep 2026 10:18:36 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>24 May 2026 02:53:39 PM</t>
+          <t>15 Sep 2026 08:43:35 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:29:56 AM</t>
+          <t>16 Sep 2026 10:18:36 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>92d 18h 51m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>114d 19h 36m</t>
+          <t>13h 35m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1207844</t>
+          <t>TKT1191679</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Phursona Sherpa</t>
+          <t>Gagan Kafle</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -6291,54 +6888,54 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Om Neupane</t>
+          <t>Case :   has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>13 Jun 2026 01:15:04 PM</t>
+          <t>15 Jun 2026 03:38:40 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>06 Jun 2026 02:40:21 PM</t>
+          <t>24 May 2026 02:53:39 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:29:30 AM</t>
+          <t>16 Sep 2026 10:29:56 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>94d 21h 14m</t>
+          <t>92d 18h 51m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>101d 19h 49m</t>
+          <t>114d 19h 36m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1209820</t>
+          <t>TKT1207844</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Sanjib Thapa Magar</t>
+          <t>Phursona Sherpa</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -6358,54 +6955,54 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : Set up box not working   has been updated by Om Neupane</t>
+          <t>Case : wifi 6  has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>13 Jun 2026 01:46:51 PM</t>
+          <t>13 Jun 2026 01:15:04 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>07 Jun 2026 09:07:12 PM</t>
+          <t>06 Jun 2026 02:40:21 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:26:14 AM</t>
+          <t>16 Sep 2026 10:29:30 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>94d 20h 39m</t>
+          <t>94d 21h 14m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>100d 13h 19m</t>
+          <t>101d 19h 49m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1334895</t>
+          <t>TKT1209820</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>DITSA TECHNOLOGY PVT. LTD</t>
+          <t>Sanjib Thapa Magar</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -6425,44 +7022,44 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6 router  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Set up box not working   has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:37:31 AM</t>
+          <t>13 Jun 2026 01:46:51 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:04:24 PM</t>
+          <t>07 Jun 2026 09:07:12 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:37:31 AM</t>
+          <t>16 Sep 2026 10:26:14 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>94d 20h 39m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>17h 33m</t>
+          <t>100d 13h 19m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1334982</t>
+          <t>TKT1334895</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Rinji Sherpa</t>
+          <t>DITSA TECHNOLOGY PVT. LTD</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -6492,22 +7089,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>Case : wifi6 router  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:35:51 AM</t>
+          <t>16 Sep 2026 10:37:31 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 06:26:14 PM</t>
+          <t>15 Sep 2026 05:04:24 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:35:51 AM</t>
+          <t>16 Sep 2026 10:37:31 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -6517,29 +7114,29 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>16h 9m</t>
+          <t>17h 33m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1334968</t>
+          <t>TKT1334982</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Pramod Pandey</t>
+          <t>Rinji Sherpa</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -6559,22 +7156,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:27:53 AM</t>
+          <t>16 Sep 2026 10:35:51 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 06:00:47 PM</t>
+          <t>15 Sep 2026 06:26:14 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:27:53 AM</t>
+          <t>16 Sep 2026 10:35:51 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -6584,7 +7181,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>16h 27m</t>
+          <t>16h 9m</t>
         </is>
       </c>
     </row>
@@ -6652,6 +7249,207 @@
       <c r="M43" s="5" t="inlineStr">
         <is>
           <t>16h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334968</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Pramod Pandey</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:27:53 AM</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:00:47 PM</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:27:53 AM</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>16h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334824</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Babu Ram Sunwar</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:13:19 PM</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:13:19 PM</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:47:17 AM</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>19h 33m</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>19h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333669</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Shankar Barahi</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:41:03 AM</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:35:12 PM</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:41:03 AM</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 5m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW29"/>
+  <dimension ref="A1:AW31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5262,10 +5262,8 @@
           <t>Babu Ram Sunwar</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9803861981</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9803861981</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -5300,10 +5298,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>27.695218</t>
-        </is>
+      <c r="Y27" s="3" t="n">
+        <v>27.695218</v>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
@@ -5355,25 +5351,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>CDB154</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.219987</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.219987</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -5459,20 +5451,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M28" s="3" t="inlineStr"/>
       <c r="N28" s="3" t="inlineStr">
         <is>
           <t>Shankar Barahi</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9841285814</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9841285814</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -5507,10 +5493,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t>27.657276</t>
-        </is>
+      <c r="Y28" s="3" t="n">
+        <v>27.657276</v>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
@@ -5566,25 +5550,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
           <t>1,9</t>
         </is>
       </c>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t>85.341635</t>
-        </is>
+      <c r="AP28" s="3" t="n">
+        <v>85.341635</v>
       </c>
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
@@ -5680,10 +5660,8 @@
           <t>Rojan Khadka</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9841027827</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9841027827</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -5722,10 +5700,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t>27.6636</t>
-        </is>
+      <c r="Y29" s="3" t="n">
+        <v>27.6636</v>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
@@ -5763,10 +5739,8 @@
           <t>Fiber wire breakage suspect</t>
         </is>
       </c>
-      <c r="AH29" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH29" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
@@ -5789,48 +5763,466 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
           <t>CDB324</t>
         </is>
       </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>85.34176</t>
-        </is>
+      <c r="AP29" s="3" t="n">
+        <v>85.34175999999999</v>
       </c>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>2h 42m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
           <t>Case : Router faulty   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS29" s="3" t="inlineStr">
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:55 AM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1332875</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Prashansa Lamichhane</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Prashansa Lamichhane</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9843467444</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:55:37 AM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9843467444</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>13 Sep 2026 06:14:45 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:55:37 AM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>Near Pranjali World School, Balaju-16, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>prashansalamichhane@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>21:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>CDB058</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT29" s="3" t="inlineStr">
-        <is>
-          <t>2h 42m</t>
-        </is>
-      </c>
-      <c r="AU29" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (In Progress)</t>
-        </is>
-      </c>
-      <c r="AV29" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router faulty   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW29" s="3" t="inlineStr">
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>2d 17h 40m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:50 AM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334603</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Danai</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Danai</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9849149003</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:56:11 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9849149003</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:56:11 PM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:50:53 AM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>27.7238</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Basnettar Tarakeshwar 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>herosudeep7@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>07:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>85.30359</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>21h 54m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>21h 54m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -5847,7 +6239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5884,7 +6276,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -5894,7 +6286,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -5905,7 +6297,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -5917,7 +6309,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>17d 17h 1m</t>
+          <t>15d 19h</t>
         </is>
       </c>
     </row>
@@ -5929,7 +6321,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>20d 10h 50m</t>
+          <t>18d 9h 10m</t>
         </is>
       </c>
     </row>
@@ -5970,14 +6362,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>11</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
@@ -6096,14 +6488,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>92.3%</t>
         </is>
       </c>
     </row>
@@ -7352,7 +7744,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -7419,14 +7811,14 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
           <t>Case : WIFI 6 upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6 upgrade  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
           <t>16 Sep 2026 11:41:03 AM</t>
@@ -7450,6 +7842,140 @@
       <c r="M46" s="3" t="inlineStr">
         <is>
           <t>1d 20h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TKT1332875</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Prashansa Lamichhane</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:55:37 AM</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>13 Sep 2026 06:14:45 PM</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:55:37 AM</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>2d 17h 40m</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334603</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Danai</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:56:11 PM</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:56:11 PM</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:50:53 AM</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>21h 54m</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>21h 54m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -5873,10 +5873,8 @@
           <t>Prashansa Lamichhane</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9843467444</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9843467444</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -5911,10 +5909,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y30" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y30" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
@@ -5970,25 +5966,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
           <t>CDB058</t>
         </is>
       </c>
-      <c r="AP30" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP30" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
@@ -6084,10 +6076,8 @@
           <t>Sudip Danai</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9849149003</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9849149003</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -6122,10 +6112,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>27.7238</t>
-        </is>
+      <c r="Y31" s="3" t="n">
+        <v>27.7238</v>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
@@ -6181,25 +6169,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>2,5</t>
         </is>
       </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>85.30359</t>
-        </is>
+      <c r="AP31" s="3" t="n">
+        <v>85.30359</v>
       </c>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -6248,7 +6232,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -7878,7 +7862,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -7945,7 +7929,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW31"/>
+  <dimension ref="A1:AW34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -6212,6 +6212,631 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:29 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334891</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Mohan krishna thapa</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Mohan krishna thapa</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9851176881</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:50:32 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9851176881</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:02:14 PM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:29:34 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Kalanki chowk, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr"/>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>05:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>CDB021</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr"/>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>15h 39m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>19h 27m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:42 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334836</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Human Harmony Nepal</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Human Harmony Nepal</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9803278325</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:22:29 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9803278325</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:22:29 PM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:42:34 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>27.73665</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Basantanagar Machhapokhari ward no:16 near SS college, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>masnepal2017@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI33" s="3" t="inlineStr"/>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>CDB532</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>85.30495</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>20h 20m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>20h 20m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:34 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>WIFI6 Router upgrade</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334862</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Bishnu Dhakal</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Bishnu Dhakal</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9841030172</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:46:44 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9841030172</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:43:24 PM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:34:32 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>27.73668</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Balaju 27.73667643205283, 85.30701387191941, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>bibekdhakal721@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>05:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>85.30701</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>19h 47m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>19h 51m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6223,7 +6848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6232,7 +6857,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6260,7 +6885,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -6270,7 +6895,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -6281,7 +6906,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.6%</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6918,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>15d 19h</t>
+          <t>14d 6h 53m</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6930,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>18d 9h 10m</t>
+          <t>16d 15h 1m</t>
         </is>
       </c>
     </row>
@@ -6346,14 +6971,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>82.4%</t>
         </is>
       </c>
     </row>
@@ -6382,14 +7007,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6472,14 +7097,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D18" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
@@ -6583,18 +7208,18 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -6606,41 +7231,41 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6652,197 +7277,153 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr"/>
-      <c r="B27" s="5" t="inlineStr"/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
       <c r="C27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>TKT1334942</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>INDIRA RANABHAT</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 08:35:54 AM</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 05:33:53 PM</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 08:35:54 AM</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>15h 2m</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1334736</t>
+          <t>TKT1334942</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Dipendra Shrestha</t>
+          <t>INDIRA RANABHAT</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -6862,22 +7443,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:14:43 AM</t>
+          <t>16 Sep 2026 08:35:54 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:19:43 PM</t>
+          <t>15 Sep 2026 05:33:53 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:14:43 AM</t>
+          <t>16 Sep 2026 08:35:54 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -6887,29 +7468,29 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>17h 55m</t>
+          <t>15h 2m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1335101</t>
+          <t>TKT1334736</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Sudip Shrestha</t>
+          <t>Dipendra Shrestha</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -6929,22 +7510,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:07:15 AM</t>
+          <t>16 Sep 2026 09:14:43 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:31:59 PM</t>
+          <t>15 Sep 2026 03:19:43 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:07:15 AM</t>
+          <t>16 Sep 2026 09:14:43 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -6954,29 +7535,29 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>12h 35m</t>
+          <t>17h 55m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1335000</t>
+          <t>TKT1335101</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Saman Shrestha</t>
+          <t>Sudip Shrestha</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -6996,22 +7577,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:44:13 AM</t>
+          <t>16 Sep 2026 09:07:15 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 06:47:39 PM</t>
+          <t>15 Sep 2026 08:31:59 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:44:13 AM</t>
+          <t>16 Sep 2026 09:07:15 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -7021,19 +7602,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>14h 56m</t>
+          <t>12h 35m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1334960</t>
+          <t>TKT1335000</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Raju Tamang</t>
+          <t>Saman Shrestha</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -7068,17 +7649,17 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:03:37 AM</t>
+          <t>16 Sep 2026 09:44:13 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:50:27 PM</t>
+          <t>15 Sep 2026 06:47:39 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:03:37 AM</t>
+          <t>16 Sep 2026 09:44:13 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -7088,19 +7669,19 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>16h 13m</t>
+          <t>14h 56m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1334610</t>
+          <t>TKT1334960</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>kran nepali</t>
+          <t>Raju Tamang</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -7110,7 +7691,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -7130,22 +7711,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:06:51 AM</t>
+          <t>16 Sep 2026 10:03:37 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:58:57 PM</t>
+          <t>15 Sep 2026 05:50:27 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:06:51 AM</t>
+          <t>16 Sep 2026 10:03:37 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -7155,19 +7736,19 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>20h 7m</t>
+          <t>16h 13m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1335114</t>
+          <t>TKT1334610</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Bishnu Bikram Khatri</t>
+          <t>kran nepali</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -7177,7 +7758,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -7197,22 +7778,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:18:36 AM</t>
+          <t>16 Sep 2026 10:06:51 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:43:35 PM</t>
+          <t>15 Sep 2026 01:58:57 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:18:36 AM</t>
+          <t>16 Sep 2026 10:06:51 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -7222,19 +7803,19 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>13h 35m</t>
+          <t>20h 7m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1191679</t>
+          <t>TKT1335114</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Gagan Kafle</t>
+          <t>Bishnu Bikram Khatri</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -7264,44 +7845,44 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Om Neupane</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>15 Jun 2026 03:38:40 PM</t>
+          <t>16 Sep 2026 10:18:36 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>24 May 2026 02:53:39 PM</t>
+          <t>15 Sep 2026 08:43:35 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:29:56 AM</t>
+          <t>16 Sep 2026 10:18:36 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>92d 18h 51m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>114d 19h 36m</t>
+          <t>13h 35m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1207844</t>
+          <t>TKT1191679</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Phursona Sherpa</t>
+          <t>Gagan Kafle</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -7331,54 +7912,54 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Om Neupane</t>
+          <t>Case :   has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>13 Jun 2026 01:15:04 PM</t>
+          <t>15 Jun 2026 03:38:40 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>06 Jun 2026 02:40:21 PM</t>
+          <t>24 May 2026 02:53:39 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:29:30 AM</t>
+          <t>16 Sep 2026 10:29:56 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>94d 21h 14m</t>
+          <t>92d 18h 51m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>101d 19h 49m</t>
+          <t>114d 19h 36m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1209820</t>
+          <t>TKT1207844</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Sanjib Thapa Magar</t>
+          <t>Phursona Sherpa</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -7398,54 +7979,54 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : Set up box not working   has been updated by Om Neupane</t>
+          <t>Case : wifi 6  has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>13 Jun 2026 01:46:51 PM</t>
+          <t>13 Jun 2026 01:15:04 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>07 Jun 2026 09:07:12 PM</t>
+          <t>06 Jun 2026 02:40:21 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:26:14 AM</t>
+          <t>16 Sep 2026 10:29:30 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>94d 20h 39m</t>
+          <t>94d 21h 14m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>100d 13h 19m</t>
+          <t>101d 19h 49m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1334895</t>
+          <t>TKT1209820</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>DITSA TECHNOLOGY PVT. LTD</t>
+          <t>Sanjib Thapa Magar</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -7465,44 +8046,44 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6 router  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Set up box not working   has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:37:31 AM</t>
+          <t>13 Jun 2026 01:46:51 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:04:24 PM</t>
+          <t>07 Jun 2026 09:07:12 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:37:31 AM</t>
+          <t>16 Sep 2026 10:26:14 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>94d 20h 39m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>17h 33m</t>
+          <t>100d 13h 19m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1334982</t>
+          <t>TKT1334895</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Rinji Sherpa</t>
+          <t>DITSA TECHNOLOGY PVT. LTD</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -7532,22 +8113,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>Case : wifi6 router  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:35:51 AM</t>
+          <t>16 Sep 2026 10:37:31 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 06:26:14 PM</t>
+          <t>15 Sep 2026 05:04:24 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:35:51 AM</t>
+          <t>16 Sep 2026 10:37:31 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -7557,29 +8138,29 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>16h 9m</t>
+          <t>17h 33m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1334968</t>
+          <t>TKT1334982</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Pramod Pandey</t>
+          <t>Rinji Sherpa</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -7599,22 +8180,22 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:27:53 AM</t>
+          <t>16 Sep 2026 10:35:51 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 06:00:47 PM</t>
+          <t>15 Sep 2026 06:26:14 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:27:53 AM</t>
+          <t>16 Sep 2026 10:35:51 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -7624,7 +8205,7 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>16h 27m</t>
+          <t>16h 9m</t>
         </is>
       </c>
     </row>
@@ -7698,22 +8279,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1334824</t>
+          <t>TKT1334968</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Babu Ram Sunwar</t>
+          <t>Pramod Pandey</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -7733,44 +8314,44 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:13:19 PM</t>
+          <t>16 Sep 2026 10:27:53 AM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:13:19 PM</t>
+          <t>15 Sep 2026 06:00:47 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:47:17 AM</t>
+          <t>16 Sep 2026 10:27:53 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>19h 33m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>19h 33m</t>
+          <t>16h 27m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1333669</t>
+          <t>TKT1334824</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Shankar Barahi</t>
+          <t>Babu Ram Sunwar</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -7800,44 +8381,44 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:41:03 AM</t>
+          <t>15 Sep 2026 04:13:19 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:35:12 PM</t>
+          <t>15 Sep 2026 04:13:19 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:41:03 AM</t>
+          <t>16 Sep 2026 11:47:17 AM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>19h 33m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1d 20h 5m</t>
+          <t>19h 33m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1332875</t>
+          <t>TKT1333669</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Prashansa Lamichhane</t>
+          <t>Shankar Barahi</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -7867,22 +8448,22 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+          <t>Case : WIFI 6 upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:55:37 AM</t>
+          <t>16 Sep 2026 11:41:03 AM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>13 Sep 2026 06:14:45 PM</t>
+          <t>14 Sep 2026 03:35:12 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:55:37 AM</t>
+          <t>16 Sep 2026 11:41:03 AM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -7892,74 +8473,275 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>2d 17h 40m</t>
+          <t>1d 20h 5m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
+          <t>TKT1332875</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Prashansa Lamichhane</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:55:37 AM</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>13 Sep 2026 06:14:45 PM</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:55:37 AM</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>2d 17h 40m</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
           <t>TKT1334603</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>Sudip Danai</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>15 Sep 2026 01:56:11 PM</t>
         </is>
       </c>
-      <c r="J48" s="3" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>15 Sep 2026 01:56:11 PM</t>
         </is>
       </c>
-      <c r="K48" s="3" t="inlineStr">
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>16 Sep 2026 11:50:53 AM</t>
         </is>
       </c>
-      <c r="L48" s="3" t="inlineStr">
+      <c r="L49" s="5" t="inlineStr">
         <is>
           <t>21h 54m</t>
         </is>
       </c>
-      <c r="M48" s="3" t="inlineStr">
+      <c r="M49" s="5" t="inlineStr">
         <is>
           <t>21h 54m</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334891</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Mohan krishna thapa</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:50:32 PM</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:02:14 PM</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:29:34 PM</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>15h 39m</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>19h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334862</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Bishnu Dhakal</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:46:44 PM</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:43:24 PM</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:34:32 PM</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>19h 47m</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>19h 51m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW34"/>
+  <dimension ref="A1:AW37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6279,10 +6279,8 @@
           <t>Mohan krishna thapa</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9851176881</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9851176881</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -6350,10 +6348,8 @@
           <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
-      <c r="AH32" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH32" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
@@ -6372,10 +6368,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
@@ -6386,7 +6380,7 @@
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
@@ -6482,10 +6476,8 @@
           <t>Human Harmony Nepal</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9803278325</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9803278325</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -6520,10 +6512,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>27.73665</t>
-        </is>
+      <c r="Y33" s="3" t="n">
+        <v>27.73665</v>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
@@ -6561,10 +6551,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH33" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH33" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI33" s="3" t="inlineStr"/>
       <c r="AJ33" s="3" t="inlineStr"/>
@@ -6579,25 +6567,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>CDB532</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>85.30495</t>
-        </is>
+      <c r="AP33" s="3" t="n">
+        <v>85.30495000000001</v>
       </c>
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
@@ -6693,10 +6677,8 @@
           <t>Bishnu Dhakal</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9841030172</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9841030172</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -6731,10 +6713,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>27.73668</t>
-        </is>
+      <c r="Y34" s="3" t="n">
+        <v>27.73668</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -6790,50 +6770,571 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>85.30701</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>85.30701000000001</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>19h 47m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>19h 51m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
           <t>Case : WIFI6 Router upgrade  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS34" s="3" t="inlineStr">
-        <is>
-          <t>19h 47m</t>
-        </is>
-      </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>19h 51m</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV34" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI6 Router upgrade  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW34" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:52 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr"/>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr"/>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr"/>
+      <c r="V35" s="3" t="inlineStr"/>
+      <c r="W35" s="3" t="inlineStr"/>
+      <c r="X35" s="3" t="inlineStr"/>
+      <c r="Y35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="inlineStr"/>
+      <c r="AA35" s="3" t="inlineStr"/>
+      <c r="AB35" s="3" t="inlineStr"/>
+      <c r="AC35" s="3" t="inlineStr"/>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr"/>
+      <c r="AF35" s="3" t="inlineStr"/>
+      <c r="AG35" s="3" t="inlineStr"/>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr"/>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr"/>
+      <c r="AM35" s="3" t="inlineStr"/>
+      <c r="AN35" s="3" t="inlineStr"/>
+      <c r="AO35" s="3" t="inlineStr"/>
+      <c r="AP35" s="3" t="inlineStr"/>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:47 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Slow internet issue</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334576</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Gyan Prasad Gairi</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Gyan Prasad Gairi</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9828422034</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:47:02 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>LTP9828422034</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:43:29 PM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:47:02 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>27.687219451997994, 85.331813780684 GPS Coordinates Nearest: CDB271 (6m Road) Map: CG Sankhmul, Kath</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>9828422034@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>09:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Sandesh Ghale</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>23h 3m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:41 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Slow internet issue</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334576</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Gyan Prasad Gairi</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Gyan Prasad Gairi</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9828422034</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:47:02 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>LTP9828422034</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:43:29 PM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:47:02 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>27.687219451997994, 85.331813780684 GPS Coordinates Nearest: CDB271 (6m Road) Map: CG Sankhmul, Kath</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>9828422034@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>09:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Sandesh Ghale</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>23h 3m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -6848,7 +7349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6885,7 +7386,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -6895,7 +7396,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -6906,7 +7407,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>61.1%</t>
         </is>
       </c>
     </row>
@@ -6918,7 +7419,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>14d 6h 53m</t>
+          <t>12d 23h 42m</t>
         </is>
       </c>
     </row>
@@ -6930,7 +7431,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>16d 15h 1m</t>
+          <t>15d 4h 50m</t>
         </is>
       </c>
     </row>
@@ -7037,74 +7538,69 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
       <c r="B14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>86.7%</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
@@ -7116,41 +7612,41 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7658,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -7185,41 +7681,41 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -7231,18 +7727,18 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -7254,41 +7750,41 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -7300,264 +7796,176 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr"/>
-      <c r="B28" s="3" t="inlineStr"/>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr"/>
+      <c r="B30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>TKT1334942</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>INDIRA RANABHAT</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 08:35:54 AM</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 05:33:53 PM</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 08:35:54 AM</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>15h 2m</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>TKT1334736</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Dipendra Shrestha</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>NETTV-No internet connection in STB</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 09:14:43 AM</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 03:19:43 PM</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 09:14:43 AM</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>17h 55m</t>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1335101</t>
+          <t>TKT1334942</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Sudip Shrestha</t>
+          <t>INDIRA RANABHAT</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -7577,22 +7985,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:07:15 AM</t>
+          <t>16 Sep 2026 08:35:54 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:31:59 PM</t>
+          <t>15 Sep 2026 05:33:53 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:07:15 AM</t>
+          <t>16 Sep 2026 08:35:54 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -7602,29 +8010,29 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>12h 35m</t>
+          <t>15h 2m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1335000</t>
+          <t>TKT1334736</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Saman Shrestha</t>
+          <t>Dipendra Shrestha</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -7644,22 +8052,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:44:13 AM</t>
+          <t>16 Sep 2026 09:14:43 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 06:47:39 PM</t>
+          <t>15 Sep 2026 03:19:43 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:44:13 AM</t>
+          <t>16 Sep 2026 09:14:43 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -7669,29 +8077,29 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>14h 56m</t>
+          <t>17h 55m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1334960</t>
+          <t>TKT1335101</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Raju Tamang</t>
+          <t>Sudip Shrestha</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -7711,22 +8119,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:03:37 AM</t>
+          <t>16 Sep 2026 09:07:15 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:50:27 PM</t>
+          <t>15 Sep 2026 08:31:59 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:03:37 AM</t>
+          <t>16 Sep 2026 09:07:15 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -7736,19 +8144,19 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>16h 13m</t>
+          <t>12h 35m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1334610</t>
+          <t>TKT1335000</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>kran nepali</t>
+          <t>Saman Shrestha</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -7758,7 +8166,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -7778,22 +8186,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:06:51 AM</t>
+          <t>16 Sep 2026 09:44:13 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:58:57 PM</t>
+          <t>15 Sep 2026 06:47:39 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:06:51 AM</t>
+          <t>16 Sep 2026 09:44:13 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -7803,19 +8211,19 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>20h 7m</t>
+          <t>14h 56m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1335114</t>
+          <t>TKT1334960</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Bishnu Bikram Khatri</t>
+          <t>Raju Tamang</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -7845,22 +8253,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:18:36 AM</t>
+          <t>16 Sep 2026 10:03:37 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:43:35 PM</t>
+          <t>15 Sep 2026 05:50:27 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:18:36 AM</t>
+          <t>16 Sep 2026 10:03:37 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -7870,19 +8278,19 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>13h 35m</t>
+          <t>16h 13m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1191679</t>
+          <t>TKT1334610</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Gagan Kafle</t>
+          <t>kran nepali</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -7892,7 +8300,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -7912,44 +8320,44 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Om Neupane</t>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>15 Jun 2026 03:38:40 PM</t>
+          <t>16 Sep 2026 10:06:51 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>24 May 2026 02:53:39 PM</t>
+          <t>15 Sep 2026 01:58:57 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:29:56 AM</t>
+          <t>16 Sep 2026 10:06:51 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>92d 18h 51m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>114d 19h 36m</t>
+          <t>20h 7m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1207844</t>
+          <t>TKT1335114</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Phursona Sherpa</t>
+          <t>Bishnu Bikram Khatri</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -7979,54 +8387,54 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Om Neupane</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>13 Jun 2026 01:15:04 PM</t>
+          <t>16 Sep 2026 10:18:36 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>06 Jun 2026 02:40:21 PM</t>
+          <t>15 Sep 2026 08:43:35 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:29:30 AM</t>
+          <t>16 Sep 2026 10:18:36 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>94d 21h 14m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>101d 19h 49m</t>
+          <t>13h 35m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1209820</t>
+          <t>TKT1191679</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Sanjib Thapa Magar</t>
+          <t>Gagan Kafle</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -8046,44 +8454,44 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : Set up box not working   has been updated by Om Neupane</t>
+          <t>Case :   has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>13 Jun 2026 01:46:51 PM</t>
+          <t>15 Jun 2026 03:38:40 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>07 Jun 2026 09:07:12 PM</t>
+          <t>24 May 2026 02:53:39 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:26:14 AM</t>
+          <t>16 Sep 2026 10:29:56 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>94d 20h 39m</t>
+          <t>92d 18h 51m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>100d 13h 19m</t>
+          <t>114d 19h 36m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1334895</t>
+          <t>TKT1207844</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>DITSA TECHNOLOGY PVT. LTD</t>
+          <t>Phursona Sherpa</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -8113,54 +8521,54 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6 router  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:37:31 AM</t>
+          <t>13 Jun 2026 01:15:04 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:04:24 PM</t>
+          <t>06 Jun 2026 02:40:21 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:37:31 AM</t>
+          <t>16 Sep 2026 10:29:30 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>94d 21h 14m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>17h 33m</t>
+          <t>101d 19h 49m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1334982</t>
+          <t>TKT1209820</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Rinji Sherpa</t>
+          <t>Sanjib Thapa Magar</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -8180,54 +8588,54 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>Case : Set up box not working   has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:35:51 AM</t>
+          <t>13 Jun 2026 01:46:51 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 06:26:14 PM</t>
+          <t>07 Jun 2026 09:07:12 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:35:51 AM</t>
+          <t>16 Sep 2026 10:26:14 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>94d 20h 39m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>16h 9m</t>
+          <t>100d 13h 19m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1334968</t>
+          <t>TKT1334895</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Pramod Pandey</t>
+          <t>DITSA TECHNOLOGY PVT. LTD</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -8247,22 +8655,22 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6 router  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:27:53 AM</t>
+          <t>16 Sep 2026 10:37:31 AM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 06:00:47 PM</t>
+          <t>15 Sep 2026 05:04:24 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:27:53 AM</t>
+          <t>16 Sep 2026 10:37:31 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -8272,29 +8680,29 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>16h 27m</t>
+          <t>17h 33m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1334968</t>
+          <t>TKT1334982</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Pramod Pandey</t>
+          <t>Rinji Sherpa</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -8314,22 +8722,22 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:27:53 AM</t>
+          <t>16 Sep 2026 10:35:51 AM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 06:00:47 PM</t>
+          <t>15 Sep 2026 06:26:14 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:27:53 AM</t>
+          <t>16 Sep 2026 10:35:51 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -8339,29 +8747,29 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>16h 27m</t>
+          <t>16h 9m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1334824</t>
+          <t>TKT1334968</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Babu Ram Sunwar</t>
+          <t>Pramod Pandey</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -8381,54 +8789,54 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:13:19 PM</t>
+          <t>16 Sep 2026 10:27:53 AM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:13:19 PM</t>
+          <t>15 Sep 2026 06:00:47 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:47:17 AM</t>
+          <t>16 Sep 2026 10:27:53 AM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>19h 33m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>19h 33m</t>
+          <t>16h 27m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1333669</t>
+          <t>TKT1334968</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Shankar Barahi</t>
+          <t>Pramod Pandey</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -8448,22 +8856,22 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:41:03 AM</t>
+          <t>16 Sep 2026 10:27:53 AM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:35:12 PM</t>
+          <t>15 Sep 2026 06:00:47 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:41:03 AM</t>
+          <t>16 Sep 2026 10:27:53 AM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -8473,19 +8881,19 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>1d 20h 5m</t>
+          <t>16h 27m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1332875</t>
+          <t>TKT1334824</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Prashansa Lamichhane</t>
+          <t>Babu Ram Sunwar</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -8515,44 +8923,44 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:55:37 AM</t>
+          <t>15 Sep 2026 04:13:19 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>13 Sep 2026 06:14:45 PM</t>
+          <t>15 Sep 2026 04:13:19 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:55:37 AM</t>
+          <t>16 Sep 2026 11:47:17 AM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>19h 33m</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>2d 17h 40m</t>
+          <t>19h 33m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1334603</t>
+          <t>TKT1333669</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Sudip Danai</t>
+          <t>Shankar Barahi</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -8567,12 +8975,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -8582,166 +8990,434 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : WIFI 6 upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:56:11 PM</t>
+          <t>16 Sep 2026 11:41:03 AM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:56:11 PM</t>
+          <t>14 Sep 2026 03:35:12 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:50:53 AM</t>
+          <t>16 Sep 2026 11:41:03 AM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>21h 54m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>21h 54m</t>
+          <t>1d 20h 5m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1334891</t>
+          <t>TKT1332875</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Mohan krishna thapa</t>
+          <t>Prashansa Lamichhane</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Ajit Shrestha</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:50:32 PM</t>
+          <t>16 Sep 2026 11:55:37 AM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:02:14 PM</t>
+          <t>13 Sep 2026 06:14:45 PM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 12:29:34 PM</t>
+          <t>16 Sep 2026 11:55:37 AM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>15h 39m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>19h 27m</t>
+          <t>2d 17h 40m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
+          <t>TKT1334603</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Sudip Danai</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:56:11 PM</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:56:11 PM</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:50:53 AM</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>21h 54m</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>21h 54m</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334891</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Mohan krishna thapa</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:50:32 PM</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:02:14 PM</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:29:34 PM</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>15h 39m</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>19h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
           <t>TKT1334862</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>Bishnu Dhakal</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>Case : WIFI6 Router upgrade  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>Case : WIFI6 Router upgrade  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>15 Sep 2026 04:46:44 PM</t>
         </is>
       </c>
-      <c r="J51" s="5" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>15 Sep 2026 04:43:24 PM</t>
         </is>
       </c>
-      <c r="K51" s="5" t="inlineStr">
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>16 Sep 2026 12:34:32 PM</t>
         </is>
       </c>
-      <c r="L51" s="5" t="inlineStr">
+      <c r="L53" s="5" t="inlineStr">
         <is>
           <t>19h 47m</t>
         </is>
       </c>
-      <c r="M51" s="5" t="inlineStr">
+      <c r="M53" s="5" t="inlineStr">
         <is>
           <t>19h 51m</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334576</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Gyan Prasad Gairi</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:47:02 PM</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:43:29 PM</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:47:02 PM</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>23h 3m</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334576</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Gyan Prasad Gairi</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Case : Slow internet issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Case : Slow internet issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:47:02 PM</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:43:29 PM</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:47:02 PM</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>23h 3m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -6983,10 +6983,8 @@
           <t>Gyan Prasad Gairi</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9828422034</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9828422034</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7021,10 +7019,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -7080,25 +7076,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>1,1</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow internet issue  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -7194,10 +7186,8 @@
           <t>Gyan Prasad Gairi</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9828422034</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9828422034</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -7232,10 +7222,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
@@ -7291,25 +7279,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>1,1</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow internet issue  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
@@ -7358,7 +7342,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9320,7 +9304,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow internet issue  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -9387,7 +9371,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Case : Slow internet issue  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW37"/>
+  <dimension ref="A1:AW38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -7322,6 +7322,217 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 1:11 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334854</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Avinash Gyalzen Lama</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Avinash Gyalzen Lama</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9803395469</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:33:49 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>9803395469</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:33:49 PM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:11:53 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>27.70509</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>Ghattekulo,Kathmandu,Near by  Kakshalaya Kindergarten School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>avi.lama009@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>06:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>CDB222</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>853000000</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>20h 38m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>20h 38m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7333,7 +7544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7342,7 +7553,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -7370,7 +7581,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -7380,7 +7591,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -7391,7 +7602,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>62.2%</t>
         </is>
       </c>
     </row>
@@ -7403,7 +7614,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>12d 23h 42m</t>
+          <t>12d 11h 3m</t>
         </is>
       </c>
     </row>
@@ -7415,7 +7626,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>15d 4h 50m</t>
+          <t>14d 13h 52m</t>
         </is>
       </c>
     </row>
@@ -7456,14 +7667,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -7600,14 +7811,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -9405,6 +9616,73 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334854</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Avinash Gyalzen Lama</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:33:49 PM</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:33:49 PM</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:11:53 PM</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>20h 38m</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>20h 38m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW38"/>
+  <dimension ref="A1:AW43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7389,10 +7389,8 @@
           <t>Avinash Gyalzen Lama</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9803395469</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9803395469</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -7427,10 +7425,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>27.70509</t>
-        </is>
+      <c r="Y38" s="3" t="n">
+        <v>27.70509</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
@@ -7486,48 +7482,1083 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>CDB222</t>
         </is>
       </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>853000000</t>
-        </is>
+      <c r="AP38" s="3" t="n">
+        <v>853000000</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>20h 38m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>20h 38m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS38" s="3" t="inlineStr">
-        <is>
-          <t>20h 38m</t>
-        </is>
-      </c>
-      <c r="AT38" s="3" t="inlineStr">
-        <is>
-          <t>20h 38m</t>
-        </is>
-      </c>
-      <c r="AU38" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV38" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 1:31 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334938</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Rajiv Bhandari</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Rajiv Bhandari</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9823722405</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:32:10 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>KLK9823722405</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:32:10 PM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:31:44 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>soyambu 5 dhara, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>9823722405@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>05:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>CDB421</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>19h 59m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>19h 59m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 1:31 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335558</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Rai</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Rai</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9840354659</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:31:25 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>9840354659</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:40:28 AM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:31:25 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t>27.69276</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Santinagar / New Baneshwor Global ime bank, shantinagar Branch, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr">
+        <is>
+          <t>rairoshan413@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>01:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>L2-1</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr">
+        <is>
+          <t>85.3471</t>
+        </is>
+      </c>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>1h 50m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 1:17 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335471</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Sarakha Human Search</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Sarakha Human Search</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9808338626</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:17:45 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9863712764</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:45:16 AM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:17:45 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.70017</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu National School,Gyawali Marg, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>sarakhasahr1453@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>02:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>L16-4</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.3415</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>2h 32m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 1:20 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334776</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Lama</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Lama</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9841664180</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:44:39 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>9841664180</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:44:39 PM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:20:12 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>27.73431</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>samakhusi  near Everest Tandoori Foodland Restaurant, tokha, kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>mktnaffa@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr"/>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>L11-3</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>85.31838</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>21h 35m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>21h 35m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 1:19 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334860</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Sangita Rai</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Sangita Rai</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9823621577</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:42:09 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9823621577</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:42:09 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:19:25 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>27.752903</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>Grande Sports Center Details from Google Maps Tokha Rd, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>sangitarae123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr"/>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>L12-3</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>85.33303</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>20h 37m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>20h 37m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -7544,7 +8575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7581,7 +8612,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -7591,7 +8622,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -7602,7 +8633,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>61.9%</t>
         </is>
       </c>
     </row>
@@ -7614,7 +8645,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>12d 11h 3m</t>
+          <t>11d 1h 19m</t>
         </is>
       </c>
     </row>
@@ -7626,7 +8657,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>14d 13h 52m</t>
+          <t>12d 22h 26m</t>
         </is>
       </c>
     </row>
@@ -7667,14 +8698,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>15</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>78.3%</t>
         </is>
       </c>
     </row>
@@ -7811,14 +8842,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>81.0%</t>
         </is>
       </c>
     </row>
@@ -9649,14 +10680,14 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 04:33:49 PM</t>
@@ -9680,6 +10711,207 @@
       <c r="M56" s="3" t="inlineStr">
         <is>
           <t>20h 38m</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334938</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Rajiv Bhandari</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:32:10 PM</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:32:10 PM</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:31:44 PM</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>19h 59m</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>19h 59m</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335558</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Rai</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:31:25 PM</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:40:28 AM</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:31:25 PM</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>1h 50m</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>TKT1335471</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Sarakha Human Search</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:17:45 PM</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:45:16 AM</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:17:45 PM</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>2h 32m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW43"/>
+  <dimension ref="A1:AW46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7592,10 +7592,8 @@
           <t>Rajiv Bhandari</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9823722405</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9823722405</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -7685,10 +7683,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
@@ -7699,7 +7695,7 @@
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
@@ -7795,10 +7791,8 @@
           <t>Roshan Rai</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9840354659</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9840354659</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -7833,10 +7827,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t>27.69276</t>
-        </is>
+      <c r="Y40" s="3" t="n">
+        <v>27.69276</v>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
@@ -7892,25 +7884,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
           <t>L2-1</t>
         </is>
       </c>
-      <c r="AP40" s="3" t="inlineStr">
-        <is>
-          <t>85.3471</t>
-        </is>
+      <c r="AP40" s="3" t="n">
+        <v>85.3471</v>
       </c>
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
@@ -8006,10 +7994,8 @@
           <t>Sarakha Human Search</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9808338626</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9808338626</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -8044,10 +8030,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t>27.70017</t>
-        </is>
+      <c r="Y41" s="3" t="n">
+        <v>27.70017</v>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
@@ -8103,25 +8087,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>L16-4</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.3415</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.3415</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
@@ -8217,10 +8197,8 @@
           <t>Sunita Lama</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9841664180</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9841664180</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -8255,10 +8233,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t>27.73431</t>
-        </is>
+      <c r="Y42" s="3" t="n">
+        <v>27.73431</v>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
@@ -8310,25 +8286,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>L11-3</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>85.31838</t>
-        </is>
+      <c r="AP42" s="3" t="n">
+        <v>85.31838</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
@@ -8424,10 +8396,8 @@
           <t>Sangita Rai</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9823621577</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9823621577</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -8462,10 +8432,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>27.752903</t>
-        </is>
+      <c r="Y43" s="3" t="n">
+        <v>27.752903</v>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
@@ -8517,48 +8485,661 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>L12-3</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>85.33303</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>85.33302999999999</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>20h 37m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>20h 37m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS43" s="3" t="inlineStr">
-        <is>
-          <t>20h 37m</t>
-        </is>
-      </c>
-      <c r="AT43" s="3" t="inlineStr">
-        <is>
-          <t>20h 37m</t>
-        </is>
-      </c>
-      <c r="AU43" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV43" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 1:36 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335555</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Joshi</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Joshi</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9841273470</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:36:54 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>9841273470</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:35:11 AM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:36:54 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>Near Vidya Sadan Secondary School (VSES) - School Mahalaxmi 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>laxmanjoshi@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>02:01 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr"/>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>2h 1m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 1:32 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334938</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Rajiv Bhandari</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Rajiv Bhandari</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9823722405</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:32:10 PM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>KLK9823722405</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:32:10 PM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:32:16 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr"/>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>soyambu 5 dhara, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>9823722405@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>05:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>CDB421</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr"/>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 1:41 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334820</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>nikhil bhattari</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>nikhil bhattari</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9742368021</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:41:26 PM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>9867838876</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:08:47 PM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:41:26 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>27.675213</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>Amarawati, Shant Marga, Kathmandu 44600 Near to Kathmandu Forestry College, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>nirajan9815392054@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>07:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>85.340226</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>21h 32m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -8575,7 +9156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8612,7 +9193,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -8622,7 +9203,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -8633,7 +9214,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>64.4%</t>
         </is>
       </c>
     </row>
@@ -8645,7 +9226,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>11d 1h 19m</t>
+          <t>9d 22h 33m</t>
         </is>
       </c>
     </row>
@@ -8657,7 +9238,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>12d 22h 26m</t>
+          <t>11d 15h 49m</t>
         </is>
       </c>
     </row>
@@ -8698,14 +9279,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -8842,14 +9423,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -10747,7 +11328,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
@@ -10814,7 +11395,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
@@ -10881,14 +11462,14 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
           <t>16 Sep 2026 01:17:45 PM</t>
@@ -10912,6 +11493,207 @@
       <c r="M59" s="5" t="inlineStr">
         <is>
           <t>2h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335555</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Joshi</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:36:54 PM</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:35:11 AM</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:36:54 PM</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>2h 1m</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334938</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Rajiv Bhandari</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:32:10 PM</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:32:10 PM</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:32:16 PM</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334820</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>nikhil bhattari</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:41:26 PM</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:08:47 PM</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:41:26 PM</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>21h 32m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW46"/>
+  <dimension ref="A1:AW48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8595,10 +8595,8 @@
           <t>Laxman Joshi</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9841273470</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9841273470</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -8688,10 +8686,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
@@ -8702,7 +8698,7 @@
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -8798,10 +8794,8 @@
           <t>Rajiv Bhandari</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9823722405</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9823722405</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -8891,10 +8885,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
@@ -8905,7 +8897,7 @@
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
@@ -9001,10 +8993,8 @@
           <t>nikhil bhattari</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9742368021</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9742368021</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -9039,10 +9029,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>27.675213</t>
-        </is>
+      <c r="Y46" s="3" t="n">
+        <v>27.675213</v>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
@@ -9098,48 +9086,462 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
           <t>3,13</t>
         </is>
       </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>85.340226</t>
-        </is>
+      <c r="AP46" s="3" t="n">
+        <v>85.340226</v>
       </c>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>21h 32m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS46" s="3" t="inlineStr">
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 1:54 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335508</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Ayushma Rani Singh</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Ayushma Rani Singh</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9843642240</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:54:29 PM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9843642240</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:09:20 AM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:54:29 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>27.67643</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>Near Big Mart, Sahyoginagar,Koteshwor, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>ayushmasingh19@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr"/>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Sameer Thapa</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>3,12</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>85.33921</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT46" s="3" t="inlineStr">
-        <is>
-          <t>21h 32m</t>
-        </is>
-      </c>
-      <c r="AU46" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV46" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW46" s="3" t="inlineStr">
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>2h 45m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 1:50 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334776</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Lama</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Lama</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9841664180</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:44:39 PM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>9841664180</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:44:39 PM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:50:42 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>27.73431</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>samakhusi  near Everest Tandoori Foodland Restaurant, tokha, kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>mktnaffa@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>08:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>L11-3</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>85.31838</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>22h 6m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>22h 6m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -9156,7 +9558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9193,7 +9595,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -9203,7 +9605,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -9214,7 +9616,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>63.8%</t>
         </is>
       </c>
     </row>
@@ -9226,7 +9628,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9d 22h 33m</t>
+          <t>9d 15h 20m</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9640,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>11d 15h 49m</t>
+          <t>11d 7h 14m</t>
         </is>
       </c>
     </row>
@@ -9279,14 +9681,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -9423,14 +9825,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -11529,7 +11931,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
@@ -11596,7 +11998,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -11663,14 +12065,14 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
           <t>16 Sep 2026 01:41:26 PM</t>
@@ -11694,6 +12096,73 @@
       <c r="M62" s="3" t="inlineStr">
         <is>
           <t>21h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334776</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Sunita Lama</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:44:39 PM</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:44:39 PM</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:50:42 PM</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>22h 6m</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>22h 6m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW48"/>
+  <dimension ref="A1:AW50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9196,10 +9196,8 @@
           <t>Ayushma Rani Singh</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9843642240</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9843642240</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -9234,10 +9232,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y47" s="3" t="inlineStr">
-        <is>
-          <t>27.67643</t>
-        </is>
+      <c r="Y47" s="3" t="n">
+        <v>27.67643</v>
       </c>
       <c r="Z47" s="3" t="inlineStr">
         <is>
@@ -9289,25 +9285,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
           <t>3,12</t>
         </is>
       </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>85.33921</t>
-        </is>
+      <c r="AP47" s="3" t="n">
+        <v>85.33920999999999</v>
       </c>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
@@ -9403,10 +9395,8 @@
           <t>Sunita Lama</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9841664180</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9841664180</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -9441,10 +9431,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>27.73431</t>
-        </is>
+      <c r="Y48" s="3" t="n">
+        <v>27.73431</v>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
@@ -9500,48 +9488,462 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
           <t>L11-3</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>85.31838</t>
-        </is>
+      <c r="AP48" s="3" t="n">
+        <v>85.31838</v>
       </c>
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>22h 6m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>22h 6m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS48" s="3" t="inlineStr">
-        <is>
-          <t>22h 6m</t>
-        </is>
-      </c>
-      <c r="AT48" s="3" t="inlineStr">
-        <is>
-          <t>22h 6m</t>
-        </is>
-      </c>
-      <c r="AU48" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV48" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 2:10 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335451</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Kushang Shrepa</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Kushang Shrepa</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9843545310</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:10:33 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9843545310</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:27:52 AM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:10:33 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Kapan,kharibot ani gumba Details from Google Maps P9Q7+2P3, Kapan Marg, Kathmandu 44600, Bagmati, Ce</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>sbawa5622@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr"/>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>L37-6</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>3h 42m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 2:06 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335607</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Gayatri Sharma</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Gayatri Sharma</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9861865462</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:06:19 PM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>9861865462</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:12:31 PM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:06:19 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>27.734026</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>P9M6+RX4, Budhanilkantha 44600 near Trijyoti Secondary School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr">
+        <is>
+          <t>01:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>L48-7</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>85.362655</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>1h 53m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -9558,7 +9960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9595,7 +9997,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -9605,7 +10007,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -9616,7 +10018,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.3%</t>
         </is>
       </c>
     </row>
@@ -9628,7 +10030,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9d 15h 20m</t>
+          <t>9d 7h 53m</t>
         </is>
       </c>
     </row>
@@ -9640,7 +10042,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>11d 7h 14m</t>
+          <t>10d 22h 32m</t>
         </is>
       </c>
     </row>
@@ -9681,14 +10083,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>76.7%</t>
         </is>
       </c>
     </row>
@@ -9825,14 +10227,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -12132,14 +12534,14 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
           <t>15 Sep 2026 03:44:39 PM</t>
@@ -12163,6 +12565,73 @@
       <c r="M63" s="5" t="inlineStr">
         <is>
           <t>22h 6m</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335607</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Gayatri Sharma</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:06:19 PM</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:12:31 PM</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:06:19 PM</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>1h 53m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW50"/>
+  <dimension ref="A1:AW55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9598,10 +9598,8 @@
           <t>Kushang Shrepa</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9843545310</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9843545310</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -9636,10 +9634,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y49" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y49" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z49" s="3" t="inlineStr">
         <is>
@@ -9691,25 +9687,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>L37-6</t>
         </is>
       </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP49" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
@@ -9805,10 +9797,8 @@
           <t>Gayatri Sharma</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9861865462</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9861865462</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -9843,10 +9833,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y50" s="3" t="inlineStr">
-        <is>
-          <t>27.734026</t>
-        </is>
+      <c r="Y50" s="3" t="n">
+        <v>27.734026</v>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
@@ -9902,48 +9890,1095 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
           <t>L48-7</t>
         </is>
       </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>85.362655</t>
-        </is>
+      <c r="AP50" s="3" t="n">
+        <v>85.362655</v>
       </c>
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>1h 53m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS50" s="3" t="inlineStr">
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 2:23 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Router faulty</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335341</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Dhimal</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Dhimal</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9803761268</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:23:14 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>BKT9803761268</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:32:15 AM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:23:14 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr"/>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>Subhakamana Party Palace - Event venue Bhaktapur 44800, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>9803761268@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>04:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Ghimire</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>L33-3</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr"/>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT50" s="3" t="inlineStr">
-        <is>
-          <t>1h 53m</t>
-        </is>
-      </c>
-      <c r="AU50" s="3" t="inlineStr">
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>4h 50m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV50" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW50" s="3" t="inlineStr">
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 2:28 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335539</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Anigeet Nakarmi</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Anigeet Nakarmi</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9860130728</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:28:08 PM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>9860130728A</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:23:39 AM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:28:08 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>27.67309</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur-9,near Sunrise Apartments, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr">
+        <is>
+          <t>anigeetnakarmi@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>03:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>CDB019</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
+          <t>85.33868</t>
+        </is>
+      </c>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>3h 4m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 2:22 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334860</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Sangita Rai</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Sangita Rai</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9823621577</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:42:09 PM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>9823621577</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:42:09 PM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:22:48 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr">
+        <is>
+          <t>27.752903</t>
+        </is>
+      </c>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>Grande Sports Center Details from Google Maps Tokha Rd, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>sangitarae123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>07:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>L12-3</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>85.33303</t>
+        </is>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>21h 40m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>21h 40m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 2:19 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334908</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Prajjwol Kandel</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Prajjwol Kandel</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9843410543</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:11:28 PM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>9849548085</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:11:28 PM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:19:15 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr">
+        <is>
+          <t>27.73678</t>
+        </is>
+      </c>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>Gongabu Kantipur English High School,Arun dairy, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr">
+        <is>
+          <t>prajjwol14@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr">
+        <is>
+          <t>07:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>L47-1</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr">
+        <is>
+          <t>85.31085</t>
+        </is>
+      </c>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>21h 7m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>21h 7m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 2:18 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334908</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Prajjwol Kandel</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Prajjwol Kandel</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9843410543</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:11:28 PM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>9849548085</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:11:28 PM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:19:15 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr">
+        <is>
+          <t>27.73678</t>
+        </is>
+      </c>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>Gongabu Kantipur English High School,Arun dairy, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr">
+        <is>
+          <t>prajjwol14@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr"/>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>07:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>L47-1</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr">
+        <is>
+          <t>85.31085</t>
+        </is>
+      </c>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>21h 7m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>21h 7m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -9960,7 +10995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9997,7 +11032,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -10007,7 +11042,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -10018,7 +11053,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -10030,7 +11065,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9d 7h 53m</t>
+          <t>8d 2h 33m</t>
         </is>
       </c>
     </row>
@@ -10042,7 +11077,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>10d 22h 32m</t>
+          <t>9d 12h 4m</t>
         </is>
       </c>
     </row>
@@ -10083,14 +11118,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>79.4%</t>
         </is>
       </c>
     </row>
@@ -10101,14 +11136,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -10227,14 +11262,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -10333,12 +11368,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -10361,18 +11396,18 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -10384,41 +11419,41 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -10430,220 +11465,176 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr"/>
-      <c r="B30" s="3" t="inlineStr"/>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr"/>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>TKT1334942</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>INDIRA RANABHAT</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 08:35:54 AM</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 05:33:53 PM</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 08:35:54 AM</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>15h 2m</t>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1334736</t>
+          <t>TKT1334942</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Dipendra Shrestha</t>
+          <t>INDIRA RANABHAT</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -10663,22 +11654,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:14:43 AM</t>
+          <t>16 Sep 2026 08:35:54 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:19:43 PM</t>
+          <t>15 Sep 2026 05:33:53 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:14:43 AM</t>
+          <t>16 Sep 2026 08:35:54 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -10688,29 +11679,29 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>17h 55m</t>
+          <t>15h 2m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1335101</t>
+          <t>TKT1334736</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Sudip Shrestha</t>
+          <t>Dipendra Shrestha</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -10730,22 +11721,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:07:15 AM</t>
+          <t>16 Sep 2026 09:14:43 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:31:59 PM</t>
+          <t>15 Sep 2026 03:19:43 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:07:15 AM</t>
+          <t>16 Sep 2026 09:14:43 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -10755,29 +11746,29 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>12h 35m</t>
+          <t>17h 55m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1335000</t>
+          <t>TKT1335101</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Saman Shrestha</t>
+          <t>Sudip Shrestha</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -10797,22 +11788,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:44:13 AM</t>
+          <t>16 Sep 2026 09:07:15 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 06:47:39 PM</t>
+          <t>15 Sep 2026 08:31:59 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:44:13 AM</t>
+          <t>16 Sep 2026 09:07:15 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -10822,19 +11813,19 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>14h 56m</t>
+          <t>12h 35m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1334960</t>
+          <t>TKT1335000</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Raju Tamang</t>
+          <t>Saman Shrestha</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -10869,17 +11860,17 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:03:37 AM</t>
+          <t>16 Sep 2026 09:44:13 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:50:27 PM</t>
+          <t>15 Sep 2026 06:47:39 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:03:37 AM</t>
+          <t>16 Sep 2026 09:44:13 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -10889,19 +11880,19 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>16h 13m</t>
+          <t>14h 56m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1334610</t>
+          <t>TKT1334960</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>kran nepali</t>
+          <t>Raju Tamang</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -10911,7 +11902,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -10931,22 +11922,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:06:51 AM</t>
+          <t>16 Sep 2026 10:03:37 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:58:57 PM</t>
+          <t>15 Sep 2026 05:50:27 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:06:51 AM</t>
+          <t>16 Sep 2026 10:03:37 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -10956,19 +11947,19 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>20h 7m</t>
+          <t>16h 13m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1335114</t>
+          <t>TKT1334610</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Bishnu Bikram Khatri</t>
+          <t>kran nepali</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -10978,7 +11969,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -10998,22 +11989,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:18:36 AM</t>
+          <t>16 Sep 2026 10:06:51 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:43:35 PM</t>
+          <t>15 Sep 2026 01:58:57 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:18:36 AM</t>
+          <t>16 Sep 2026 10:06:51 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -11023,19 +12014,19 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>13h 35m</t>
+          <t>20h 7m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1191679</t>
+          <t>TKT1335114</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Gagan Kafle</t>
+          <t>Bishnu Bikram Khatri</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -11065,44 +12056,44 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Om Neupane</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>15 Jun 2026 03:38:40 PM</t>
+          <t>16 Sep 2026 10:18:36 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>24 May 2026 02:53:39 PM</t>
+          <t>15 Sep 2026 08:43:35 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:29:56 AM</t>
+          <t>16 Sep 2026 10:18:36 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>92d 18h 51m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>114d 19h 36m</t>
+          <t>13h 35m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1207844</t>
+          <t>TKT1191679</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Phursona Sherpa</t>
+          <t>Gagan Kafle</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -11132,54 +12123,54 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Om Neupane</t>
+          <t>Case :   has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>13 Jun 2026 01:15:04 PM</t>
+          <t>15 Jun 2026 03:38:40 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>06 Jun 2026 02:40:21 PM</t>
+          <t>24 May 2026 02:53:39 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:29:30 AM</t>
+          <t>16 Sep 2026 10:29:56 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>94d 21h 14m</t>
+          <t>92d 18h 51m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>101d 19h 49m</t>
+          <t>114d 19h 36m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1209820</t>
+          <t>TKT1207844</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Sanjib Thapa Magar</t>
+          <t>Phursona Sherpa</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -11199,54 +12190,54 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : Set up box not working   has been updated by Om Neupane</t>
+          <t>Case : wifi 6  has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>13 Jun 2026 01:46:51 PM</t>
+          <t>13 Jun 2026 01:15:04 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>07 Jun 2026 09:07:12 PM</t>
+          <t>06 Jun 2026 02:40:21 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:26:14 AM</t>
+          <t>16 Sep 2026 10:29:30 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>94d 20h 39m</t>
+          <t>94d 21h 14m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>100d 13h 19m</t>
+          <t>101d 19h 49m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1334895</t>
+          <t>TKT1209820</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>DITSA TECHNOLOGY PVT. LTD</t>
+          <t>Sanjib Thapa Magar</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -11266,44 +12257,44 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6 router  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Set up box not working   has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:37:31 AM</t>
+          <t>13 Jun 2026 01:46:51 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:04:24 PM</t>
+          <t>07 Jun 2026 09:07:12 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:37:31 AM</t>
+          <t>16 Sep 2026 10:26:14 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>94d 20h 39m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>17h 33m</t>
+          <t>100d 13h 19m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1334982</t>
+          <t>TKT1334895</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Rinji Sherpa</t>
+          <t>DITSA TECHNOLOGY PVT. LTD</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -11333,22 +12324,22 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>Case : wifi6 router  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:35:51 AM</t>
+          <t>16 Sep 2026 10:37:31 AM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 06:26:14 PM</t>
+          <t>15 Sep 2026 05:04:24 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:35:51 AM</t>
+          <t>16 Sep 2026 10:37:31 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -11358,29 +12349,29 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>16h 9m</t>
+          <t>17h 33m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1334968</t>
+          <t>TKT1334982</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Pramod Pandey</t>
+          <t>Rinji Sherpa</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -11400,22 +12391,22 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:27:53 AM</t>
+          <t>16 Sep 2026 10:35:51 AM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 06:00:47 PM</t>
+          <t>15 Sep 2026 06:26:14 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:27:53 AM</t>
+          <t>16 Sep 2026 10:35:51 AM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -11425,7 +12416,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>16h 27m</t>
+          <t>16h 9m</t>
         </is>
       </c>
     </row>
@@ -11499,22 +12490,22 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1334824</t>
+          <t>TKT1334968</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Babu Ram Sunwar</t>
+          <t>Pramod Pandey</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -11534,44 +12525,44 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:13:19 PM</t>
+          <t>16 Sep 2026 10:27:53 AM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:13:19 PM</t>
+          <t>15 Sep 2026 06:00:47 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:47:17 AM</t>
+          <t>16 Sep 2026 10:27:53 AM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>19h 33m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>19h 33m</t>
+          <t>16h 27m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1333669</t>
+          <t>TKT1334824</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Shankar Barahi</t>
+          <t>Babu Ram Sunwar</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -11601,44 +12592,44 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:41:03 AM</t>
+          <t>15 Sep 2026 04:13:19 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:35:12 PM</t>
+          <t>15 Sep 2026 04:13:19 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:41:03 AM</t>
+          <t>16 Sep 2026 11:47:17 AM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>19h 33m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>1d 20h 5m</t>
+          <t>19h 33m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1332875</t>
+          <t>TKT1333669</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Prashansa Lamichhane</t>
+          <t>Shankar Barahi</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -11668,22 +12659,22 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+          <t>Case : WIFI 6 upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:55:37 AM</t>
+          <t>16 Sep 2026 11:41:03 AM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>13 Sep 2026 06:14:45 PM</t>
+          <t>14 Sep 2026 03:35:12 PM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:55:37 AM</t>
+          <t>16 Sep 2026 11:41:03 AM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -11693,19 +12684,19 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>2d 17h 40m</t>
+          <t>1d 20h 5m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1334603</t>
+          <t>TKT1332875</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Sudip Danai</t>
+          <t>Prashansa Lamichhane</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -11720,12 +12711,12 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -11735,54 +12726,54 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:56:11 PM</t>
+          <t>16 Sep 2026 11:55:37 AM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:56:11 PM</t>
+          <t>13 Sep 2026 06:14:45 PM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:50:53 AM</t>
+          <t>16 Sep 2026 11:55:37 AM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>21h 54m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>21h 54m</t>
+          <t>2d 17h 40m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1334891</t>
+          <t>TKT1334603</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Mohan krishna thapa</t>
+          <t>Sudip Danai</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -11802,54 +12793,54 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Ajit Shrestha</t>
+          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:50:32 PM</t>
+          <t>15 Sep 2026 01:56:11 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:02:14 PM</t>
+          <t>15 Sep 2026 01:56:11 PM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 12:29:34 PM</t>
+          <t>16 Sep 2026 11:50:53 AM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>15h 39m</t>
+          <t>21h 54m</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>19h 27m</t>
+          <t>21h 54m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1334862</t>
+          <t>TKT1334891</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Bishnu Dhakal</t>
+          <t>Mohan krishna thapa</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -11869,64 +12860,64 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router upgrade  has been updated by Sunil Chaudhary</t>
+          <t>Case : IPTV Issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:46:44 PM</t>
+          <t>15 Sep 2026 08:50:32 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:43:24 PM</t>
+          <t>15 Sep 2026 05:02:14 PM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 12:34:32 PM</t>
+          <t>16 Sep 2026 12:29:34 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>19h 47m</t>
+          <t>15h 39m</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>19h 51m</t>
+          <t>19h 27m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1334576</t>
+          <t>TKT1334862</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Gyan Prasad Gairi</t>
+          <t>Bishnu Dhakal</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -11936,32 +12927,32 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow internet issue  has been updated by Rajesh Maharjan</t>
+          <t>Case : WIFI6 Router upgrade  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 12:47:02 PM</t>
+          <t>15 Sep 2026 04:46:44 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:43:29 PM</t>
+          <t>15 Sep 2026 04:43:24 PM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 12:47:02 PM</t>
+          <t>16 Sep 2026 12:34:32 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>19h 47m</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>23h 3m</t>
+          <t>19h 51m</t>
         </is>
       </c>
     </row>
@@ -12035,32 +13026,32 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1334854</t>
+          <t>TKT1334576</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Avinash Gyalzen Lama</t>
+          <t>Gyan Prasad Gairi</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -12070,44 +13061,44 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+          <t>Case : Slow internet issue  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:33:49 PM</t>
+          <t>16 Sep 2026 12:47:02 PM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:33:49 PM</t>
+          <t>15 Sep 2026 01:43:29 PM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:11:53 PM</t>
+          <t>16 Sep 2026 12:47:02 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>20h 38m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>20h 38m</t>
+          <t>23h 3m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1334938</t>
+          <t>TKT1334854</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Rajiv Bhandari</t>
+          <t>Avinash Gyalzen Lama</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -12122,12 +13113,12 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -12137,44 +13128,44 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:32:10 PM</t>
+          <t>15 Sep 2026 04:33:49 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:32:10 PM</t>
+          <t>15 Sep 2026 04:33:49 PM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:31:44 PM</t>
+          <t>16 Sep 2026 01:11:53 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>19h 59m</t>
+          <t>20h 38m</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>19h 59m</t>
+          <t>20h 38m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1335558</t>
+          <t>TKT1334938</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Roshan Rai</t>
+          <t>Rajiv Bhandari</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -12204,44 +13195,44 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:31:25 PM</t>
+          <t>15 Sep 2026 05:32:10 PM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:40:28 AM</t>
+          <t>15 Sep 2026 05:32:10 PM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:31:25 PM</t>
+          <t>16 Sep 2026 01:31:44 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>19h 59m</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1h 50m</t>
+          <t>19h 59m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1335471</t>
+          <t>TKT1335558</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Sarakha Human Search</t>
+          <t>Roshan Rai</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -12271,22 +13262,22 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:17:45 PM</t>
+          <t>16 Sep 2026 01:31:25 PM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:45:16 AM</t>
+          <t>16 Sep 2026 11:40:28 AM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:17:45 PM</t>
+          <t>16 Sep 2026 01:31:25 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
@@ -12296,19 +13287,19 @@
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>2h 32m</t>
+          <t>1h 50m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TKT1335555</t>
+          <t>TKT1335471</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Laxman Joshi</t>
+          <t>Sarakha Human Search</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -12338,22 +13329,22 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:36:54 PM</t>
+          <t>16 Sep 2026 01:17:45 PM</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:35:11 AM</t>
+          <t>16 Sep 2026 10:45:16 AM</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:36:54 PM</t>
+          <t>16 Sep 2026 01:17:45 PM</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
@@ -12363,19 +13354,19 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>2h 1m</t>
+          <t>2h 32m</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>TKT1334938</t>
+          <t>TKT1335555</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Rajiv Bhandari</t>
+          <t>Laxman Joshi</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -12390,12 +13381,12 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -12405,44 +13396,44 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:32:10 PM</t>
+          <t>16 Sep 2026 01:36:54 PM</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:32:10 PM</t>
+          <t>16 Sep 2026 11:35:11 AM</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:32:16 PM</t>
+          <t>16 Sep 2026 01:36:54 PM</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>2h 1m</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TKT1334820</t>
+          <t>TKT1334938</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>nikhil bhattari</t>
+          <t>Rajiv Bhandari</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -12457,12 +13448,12 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -12472,44 +13463,44 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:41:26 PM</t>
+          <t>15 Sep 2026 05:32:10 PM</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:08:47 PM</t>
+          <t>15 Sep 2026 05:32:10 PM</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:41:26 PM</t>
+          <t>16 Sep 2026 01:32:16 PM</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>21h 32m</t>
+          <t>20h</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>TKT1334776</t>
+          <t>TKT1334820</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Sunita Lama</t>
+          <t>nikhil bhattari</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -12524,12 +13515,12 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -12539,99 +13530,501 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:44:39 PM</t>
+          <t>16 Sep 2026 01:41:26 PM</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:44:39 PM</t>
+          <t>15 Sep 2026 04:08:47 PM</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:50:42 PM</t>
+          <t>16 Sep 2026 01:41:26 PM</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>22h 6m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>22h 6m</t>
+          <t>21h 32m</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
+          <t>TKT1334776</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Lama</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:44:39 PM</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:44:39 PM</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:50:42 PM</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>22h 6m</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>22h 6m</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
           <t>TKT1335607</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>Gayatri Sharma</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
+      <c r="I65" s="5" t="inlineStr">
         <is>
           <t>16 Sep 2026 02:06:19 PM</t>
         </is>
       </c>
-      <c r="J64" s="3" t="inlineStr">
+      <c r="J65" s="5" t="inlineStr">
         <is>
           <t>16 Sep 2026 12:12:31 PM</t>
         </is>
       </c>
-      <c r="K64" s="3" t="inlineStr">
+      <c r="K65" s="5" t="inlineStr">
         <is>
           <t>16 Sep 2026 02:06:19 PM</t>
         </is>
       </c>
-      <c r="L64" s="3" t="inlineStr">
+      <c r="L65" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M64" s="3" t="inlineStr">
+      <c r="M65" s="5" t="inlineStr">
         <is>
           <t>1h 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335341</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Dhimal</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:23:14 PM</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:32:15 AM</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:23:14 PM</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>4h 50m</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>TKT1335539</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Anigeet Nakarmi</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:28:08 PM</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:23:39 AM</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:28:08 PM</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>3h 4m</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334860</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Sangita Rai</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:42:09 PM</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:42:09 PM</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:22:48 PM</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>21h 40m</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>21h 40m</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334908</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Prajjwol Kandel</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:11:28 PM</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:11:28 PM</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:19:15 PM</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>21h 7m</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>21h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334908</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Prajjwol Kandel</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:11:28 PM</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:11:28 PM</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:19:15 PM</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>21h 7m</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>21h 7m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW55"/>
+  <dimension ref="A1:AW56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10000,10 +10000,8 @@
           <t>Roshan Dhimal</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9803761268</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9803761268</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -10075,10 +10073,8 @@
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="AH51" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH51" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI51" s="3" t="inlineStr">
         <is>
@@ -10097,10 +10093,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
@@ -10111,7 +10105,7 @@
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
@@ -10207,10 +10201,8 @@
           <t>Anigeet Nakarmi</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9860130728</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9860130728</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -10245,10 +10237,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y52" s="3" t="inlineStr">
-        <is>
-          <t>27.67309</t>
-        </is>
+      <c r="Y52" s="3" t="n">
+        <v>27.67309</v>
       </c>
       <c r="Z52" s="3" t="inlineStr">
         <is>
@@ -10304,25 +10294,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
           <t>CDB019</t>
         </is>
       </c>
-      <c r="AP52" s="3" t="inlineStr">
-        <is>
-          <t>85.33868</t>
-        </is>
+      <c r="AP52" s="3" t="n">
+        <v>85.33868</v>
       </c>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
@@ -10418,10 +10404,8 @@
           <t>Sangita Rai</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9823621577</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9823621577</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -10456,10 +10440,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y53" s="3" t="inlineStr">
-        <is>
-          <t>27.752903</t>
-        </is>
+      <c r="Y53" s="3" t="n">
+        <v>27.752903</v>
       </c>
       <c r="Z53" s="3" t="inlineStr">
         <is>
@@ -10515,25 +10497,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
           <t>L12-3</t>
         </is>
       </c>
-      <c r="AP53" s="3" t="inlineStr">
-        <is>
-          <t>85.33303</t>
-        </is>
+      <c r="AP53" s="3" t="n">
+        <v>85.33302999999999</v>
       </c>
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
@@ -10619,20 +10597,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M54" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M54" s="3" t="inlineStr"/>
       <c r="N54" s="3" t="inlineStr">
         <is>
           <t>Prajjwol Kandel</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9843410543</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9843410543</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -10667,10 +10639,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y54" s="3" t="inlineStr">
-        <is>
-          <t>27.73678</t>
-        </is>
+      <c r="Y54" s="3" t="n">
+        <v>27.73678</v>
       </c>
       <c r="Z54" s="3" t="inlineStr">
         <is>
@@ -10726,25 +10696,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
           <t>L47-1</t>
         </is>
       </c>
-      <c r="AP54" s="3" t="inlineStr">
-        <is>
-          <t>85.31085</t>
-        </is>
+      <c r="AP54" s="3" t="n">
+        <v>85.31085</v>
       </c>
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
@@ -10830,20 +10796,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M55" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M55" s="3" t="inlineStr"/>
       <c r="N55" s="3" t="inlineStr">
         <is>
           <t>Prajjwol Kandel</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9843410543</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9843410543</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -10878,10 +10838,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y55" s="3" t="inlineStr">
-        <is>
-          <t>27.73678</t>
-        </is>
+      <c r="Y55" s="3" t="n">
+        <v>27.73678</v>
       </c>
       <c r="Z55" s="3" t="inlineStr">
         <is>
@@ -10937,48 +10895,251 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
           <t>L47-1</t>
         </is>
       </c>
-      <c r="AP55" s="3" t="inlineStr">
-        <is>
-          <t>85.31085</t>
-        </is>
+      <c r="AP55" s="3" t="n">
+        <v>85.31085</v>
       </c>
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>21h 7m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>21h 7m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS55" s="3" t="inlineStr">
-        <is>
-          <t>21h 7m</t>
-        </is>
-      </c>
-      <c r="AT55" s="3" t="inlineStr">
-        <is>
-          <t>21h 7m</t>
-        </is>
-      </c>
-      <c r="AU55" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV55" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 2:34 PM</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335308</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Nabaraj Pokharel</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>Nabaraj Pokharel</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>9851042928</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 08:59:52 AM</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>9851042928</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 08:59:52 AM</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:34:32 PM</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y56" s="3" t="inlineStr">
+        <is>
+          <t>27.7709</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC56" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="inlineStr"/>
+      <c r="AE56" s="3" t="inlineStr">
+        <is>
+          <t>Hello Kids Academy Montessori School Details from Google Maps Q9C3+32Q, Budhanilkantha 44600 , Bagma</t>
+        </is>
+      </c>
+      <c r="AF56" s="3" t="inlineStr">
+        <is>
+          <t>pokharelnaba1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="inlineStr"/>
+      <c r="AI56" s="3" t="inlineStr"/>
+      <c r="AJ56" s="3" t="inlineStr"/>
+      <c r="AK56" s="3" t="inlineStr"/>
+      <c r="AL56" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>L15-8</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr">
+        <is>
+          <t>85.3504</t>
+        </is>
+      </c>
+      <c r="AQ56" s="3" t="inlineStr"/>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>5h 34m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>5h 34m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -11004,7 +11165,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -11032,7 +11193,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
@@ -11053,7 +11214,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>
@@ -11118,14 +11279,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>27</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>77.1%</t>
         </is>
       </c>
     </row>
@@ -11262,14 +11423,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>26</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>78.8%</t>
         </is>
       </c>
     </row>
@@ -13726,7 +13887,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
@@ -13793,7 +13954,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -13860,7 +14021,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
@@ -13927,7 +14088,7 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -13994,7 +14155,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW56"/>
+  <dimension ref="A1:AW58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -11005,10 +11005,8 @@
           <t>Nabaraj Pokharel</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>9851042928</t>
-        </is>
+      <c r="O56" s="3" t="n">
+        <v>9851042928</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
@@ -11043,10 +11041,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y56" s="3" t="inlineStr">
-        <is>
-          <t>27.7709</t>
-        </is>
+      <c r="Y56" s="3" t="n">
+        <v>27.7709</v>
       </c>
       <c r="Z56" s="3" t="inlineStr">
         <is>
@@ -11098,50 +11094,460 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN56" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
           <t>L15-8</t>
         </is>
       </c>
-      <c r="AP56" s="3" t="inlineStr">
-        <is>
-          <t>85.3504</t>
-        </is>
+      <c r="AP56" s="3" t="n">
+        <v>85.35039999999999</v>
       </c>
       <c r="AQ56" s="3" t="inlineStr"/>
       <c r="AR56" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>5h 34m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>5h 34m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS56" s="3" t="inlineStr">
-        <is>
-          <t>5h 34m</t>
-        </is>
-      </c>
-      <c r="AT56" s="3" t="inlineStr">
-        <is>
-          <t>5h 34m</t>
-        </is>
-      </c>
-      <c r="AU56" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV56" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW56" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 2:53 PM</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Frequent disconnection</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335518</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>kritigya katwal</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>kritigya katwal</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>9808375353</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:59:23 AM</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>CHB9808375353</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:14:50 AM</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:53:17 PM</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y57" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA57" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB57" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC57" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD57" s="3" t="inlineStr"/>
+      <c r="AE57" s="3" t="inlineStr">
+        <is>
+          <t>27.71392775653189, 85.36296487776697, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF57" s="3" t="inlineStr">
+        <is>
+          <t>9823827313@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG57" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH57" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI57" s="3" t="inlineStr"/>
+      <c r="AJ57" s="3" t="inlineStr"/>
+      <c r="AK57" s="3" t="inlineStr"/>
+      <c r="AL57" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM57" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN57" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO57" s="3" t="inlineStr">
+        <is>
+          <t>L29-5</t>
+        </is>
+      </c>
+      <c r="AP57" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ57" s="3" t="inlineStr"/>
+      <c r="AR57" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>2h 53m</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>3h 38m</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 2:49 PM</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : ROUTER UPGRADE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>ROUTER UPGRADE</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335478</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Bikash Sakhya</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>Bikash Sakhya</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>9823045668</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr"/>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:49:04 PM</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>9823045668</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:50:07 AM</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:49:04 PM</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y58" s="3" t="inlineStr"/>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA58" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB58" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC58" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD58" s="3" t="inlineStr"/>
+      <c r="AE58" s="3" t="inlineStr">
+        <is>
+          <t>Near Anukaran Traders and Suppliers Details from Google Maps M9JX+H34, Madhyapur Thimi 44600, Bagmat</t>
+        </is>
+      </c>
+      <c r="AF58" s="3" t="inlineStr">
+        <is>
+          <t>bikas19791109@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG58" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH58" s="3" t="inlineStr"/>
+      <c r="AI58" s="3" t="inlineStr">
+        <is>
+          <t>03:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ58" s="3" t="inlineStr"/>
+      <c r="AK58" s="3" t="inlineStr"/>
+      <c r="AL58" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM58" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN58" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO58" s="3" t="inlineStr">
+        <is>
+          <t>L35-4</t>
+        </is>
+      </c>
+      <c r="AP58" s="3" t="inlineStr"/>
+      <c r="AQ58" s="3" t="inlineStr"/>
+      <c r="AR58" s="3" t="inlineStr">
+        <is>
+          <t>Case : ROUTER UPGRADE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT58" s="3" t="inlineStr">
+        <is>
+          <t>3h 58m</t>
+        </is>
+      </c>
+      <c r="AU58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV58" s="3" t="inlineStr">
+        <is>
+          <t>Case : ROUTER UPGRADE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -11156,7 +11562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -11165,7 +11571,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -11193,7 +11599,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -11203,7 +11609,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -11214,7 +11620,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>64.9%</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11632,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8d 2h 33m</t>
+          <t>7d 21h 18m</t>
         </is>
       </c>
     </row>
@@ -11238,7 +11644,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>9d 12h 4m</t>
+          <t>9d 6h 1m</t>
         </is>
       </c>
     </row>
@@ -11279,14 +11685,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -11297,14 +11703,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -11423,14 +11829,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>79.4%</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11921,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>0</v>
@@ -14189,6 +14595,73 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>TKT1335478</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Bikash Sakhya</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Case : ROUTER UPGRADE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Case : ROUTER UPGRADE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:49:04 PM</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:50:07 AM</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:49:04 PM</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>3h 58m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -11204,10 +11204,8 @@
           <t>kritigya katwal</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>9808375353</t>
-        </is>
+      <c r="O57" s="3" t="n">
+        <v>9808375353</v>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
@@ -11242,10 +11240,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y57" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z57" s="3" t="inlineStr">
         <is>
@@ -11283,10 +11279,8 @@
           <t>Router Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="AH57" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH57" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI57" s="3" t="inlineStr"/>
       <c r="AJ57" s="3" t="inlineStr"/>
@@ -11301,25 +11295,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN57" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN57" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
           <t>L29-5</t>
         </is>
       </c>
-      <c r="AP57" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ57" s="3" t="inlineStr"/>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>Case : Frequent disconnection   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
@@ -11405,20 +11395,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M58" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M58" s="3" t="inlineStr"/>
       <c r="N58" s="3" t="inlineStr">
         <is>
           <t>Bikash Sakhya</t>
         </is>
       </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>9823045668</t>
-        </is>
+      <c r="O58" s="3" t="n">
+        <v>9823045668</v>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
@@ -11508,10 +11492,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN58" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN58" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
@@ -11522,7 +11504,7 @@
       <c r="AQ58" s="3" t="inlineStr"/>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>Case : ROUTER UPGRADE  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
@@ -11571,7 +11553,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -14628,7 +14610,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Case : ROUTER UPGRADE  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW58"/>
+  <dimension ref="A1:AW62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -11533,6 +11533,842 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 3:27 PM</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334489</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Suvash Timilsina</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>Suvash Timilsina</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>9841482651</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:27:24 PM</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>9841482651</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:39:16 PM</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:27:24 PM</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y59" s="3" t="inlineStr">
+        <is>
+          <t>27.746311</t>
+        </is>
+      </c>
+      <c r="Z59" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA59" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB59" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC59" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD59" s="3" t="inlineStr"/>
+      <c r="AE59" s="3" t="inlineStr">
+        <is>
+          <t>Nayapati, Gokarneshwor 44600, near chyau factory, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF59" s="3" t="inlineStr">
+        <is>
+          <t>9841482651@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG59" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH59" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI59" s="3" t="inlineStr">
+        <is>
+          <t>12:48 hour</t>
+        </is>
+      </c>
+      <c r="AJ59" s="3" t="inlineStr"/>
+      <c r="AK59" s="3" t="inlineStr"/>
+      <c r="AL59" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM59" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN59" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO59" s="3" t="inlineStr">
+        <is>
+          <t>1,7</t>
+        </is>
+      </c>
+      <c r="AP59" s="3" t="inlineStr">
+        <is>
+          <t>85.408967</t>
+        </is>
+      </c>
+      <c r="AQ59" s="3" t="inlineStr"/>
+      <c r="AR59" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 48m</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV59" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW59" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 3:28 PM</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335605</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>Sachin Magar</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>Sachin Magar</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>9849737950</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr"/>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:10:18 PM</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr"/>
+      <c r="T60" s="3" t="inlineStr"/>
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>9849737950</t>
+        </is>
+      </c>
+      <c r="V60" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:10:18 PM</t>
+        </is>
+      </c>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:28:31 PM</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y60" s="3" t="inlineStr">
+        <is>
+          <t>27.75371</t>
+        </is>
+      </c>
+      <c r="Z60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA60" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB60" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC60" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD60" s="3" t="inlineStr"/>
+      <c r="AE60" s="3" t="inlineStr">
+        <is>
+          <t>Near to Golfutar,Kathmandu - Near to Golfutar,Kathmandu, Kathmandu, Bagmati, Central, Nepa, Bagmati,</t>
+        </is>
+      </c>
+      <c r="AF60" s="3" t="inlineStr">
+        <is>
+          <t>sachinmgr663@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG60" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH60" s="3" t="inlineStr"/>
+      <c r="AI60" s="3" t="inlineStr">
+        <is>
+          <t>03:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ60" s="3" t="inlineStr"/>
+      <c r="AK60" s="3" t="inlineStr"/>
+      <c r="AL60" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM60" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN60" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO60" s="3" t="inlineStr">
+        <is>
+          <t>3,9</t>
+        </is>
+      </c>
+      <c r="AP60" s="3" t="inlineStr">
+        <is>
+          <t>85.34744</t>
+        </is>
+      </c>
+      <c r="AQ60" s="3" t="inlineStr"/>
+      <c r="AR60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
+        <is>
+          <t>3h 18m</t>
+        </is>
+      </c>
+      <c r="AT60" s="3" t="inlineStr">
+        <is>
+          <t>3h 18m</t>
+        </is>
+      </c>
+      <c r="AU60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 3:27 PM</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335605</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>Sachin Magar</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>Sachin Magar</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>9849737950</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr"/>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:10:18 PM</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr"/>
+      <c r="T61" s="3" t="inlineStr"/>
+      <c r="U61" s="3" t="inlineStr">
+        <is>
+          <t>9849737950</t>
+        </is>
+      </c>
+      <c r="V61" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:10:18 PM</t>
+        </is>
+      </c>
+      <c r="W61" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:28:31 PM</t>
+        </is>
+      </c>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y61" s="3" t="inlineStr">
+        <is>
+          <t>27.75371</t>
+        </is>
+      </c>
+      <c r="Z61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA61" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB61" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC61" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD61" s="3" t="inlineStr"/>
+      <c r="AE61" s="3" t="inlineStr">
+        <is>
+          <t>Near to Golfutar,Kathmandu - Near to Golfutar,Kathmandu, Kathmandu, Bagmati, Central, Nepa, Bagmati,</t>
+        </is>
+      </c>
+      <c r="AF61" s="3" t="inlineStr">
+        <is>
+          <t>sachinmgr663@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG61" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH61" s="3" t="inlineStr"/>
+      <c r="AI61" s="3" t="inlineStr">
+        <is>
+          <t>03:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ61" s="3" t="inlineStr"/>
+      <c r="AK61" s="3" t="inlineStr"/>
+      <c r="AL61" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM61" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN61" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO61" s="3" t="inlineStr">
+        <is>
+          <t>3,9</t>
+        </is>
+      </c>
+      <c r="AP61" s="3" t="inlineStr">
+        <is>
+          <t>85.34744</t>
+        </is>
+      </c>
+      <c r="AQ61" s="3" t="inlineStr"/>
+      <c r="AR61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS61" s="3" t="inlineStr">
+        <is>
+          <t>3h 18m</t>
+        </is>
+      </c>
+      <c r="AT61" s="3" t="inlineStr">
+        <is>
+          <t>3h 18m</t>
+        </is>
+      </c>
+      <c r="AU61" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 3:26 PM</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335663</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>Salina Alemagar</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>Salina Alemagar</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>9841347466</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q62" s="3" t="inlineStr"/>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:51:50 PM</t>
+        </is>
+      </c>
+      <c r="S62" s="3" t="inlineStr"/>
+      <c r="T62" s="3" t="inlineStr"/>
+      <c r="U62" s="3" t="inlineStr">
+        <is>
+          <t>9841347466</t>
+        </is>
+      </c>
+      <c r="V62" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:51:50 PM</t>
+        </is>
+      </c>
+      <c r="W62" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:26:43 PM</t>
+        </is>
+      </c>
+      <c r="X62" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y62" s="3" t="inlineStr"/>
+      <c r="Z62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA62" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB62" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC62" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD62" s="3" t="inlineStr"/>
+      <c r="AE62" s="3" t="inlineStr">
+        <is>
+          <t>Samakhusi  Srijanabchowk, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF62" s="3" t="inlineStr"/>
+      <c r="AG62" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH62" s="3" t="inlineStr"/>
+      <c r="AI62" s="3" t="inlineStr">
+        <is>
+          <t>02:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ62" s="3" t="inlineStr"/>
+      <c r="AK62" s="3" t="inlineStr"/>
+      <c r="AL62" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM62" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN62" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO62" s="3" t="inlineStr">
+        <is>
+          <t>L52-2</t>
+        </is>
+      </c>
+      <c r="AP62" s="3" t="inlineStr"/>
+      <c r="AQ62" s="3" t="inlineStr"/>
+      <c r="AR62" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS62" s="3" t="inlineStr">
+        <is>
+          <t>2h 34m</t>
+        </is>
+      </c>
+      <c r="AT62" s="3" t="inlineStr">
+        <is>
+          <t>2h 34m</t>
+        </is>
+      </c>
+      <c r="AU62" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV62" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW62" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11544,7 +12380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -11553,7 +12389,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -11581,7 +12417,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
@@ -11591,7 +12427,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -11602,7 +12438,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>67.2%</t>
         </is>
       </c>
     </row>
@@ -11614,7 +12450,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7d 21h 18m</t>
+          <t>7d 3h 3m</t>
         </is>
       </c>
     </row>
@@ -11626,7 +12462,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>9d 6h 1m</t>
+          <t>8d 9h 14m</t>
         </is>
       </c>
     </row>
@@ -11667,14 +12503,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>79.5%</t>
         </is>
       </c>
     </row>
@@ -11685,14 +12521,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -11811,14 +12647,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>81.1%</t>
         </is>
       </c>
     </row>
@@ -11880,10 +12716,10 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -14644,6 +15480,274 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334489</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Suvash Timilsina</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:27:24 PM</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:39:16 PM</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:27:24 PM</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 48m</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>TKT1335605</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Sachin Magar</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:10:18 PM</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:10:18 PM</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:28:31 PM</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>3h 18m</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>3h 18m</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335605</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Sachin Magar</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:10:18 PM</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:10:18 PM</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:28:31 PM</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>3h 18m</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>3h 18m</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>TKT1335663</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Salina Alemagar</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:51:50 PM</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 12:51:50 PM</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:26:43 PM</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>2h 34m</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>2h 34m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW62"/>
+  <dimension ref="A1:AW64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -11600,10 +11600,8 @@
           <t>Suvash Timilsina</t>
         </is>
       </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>9841482651</t>
-        </is>
+      <c r="O59" s="3" t="n">
+        <v>9841482651</v>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
@@ -11638,10 +11636,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y59" s="3" t="inlineStr">
-        <is>
-          <t>27.746311</t>
-        </is>
+      <c r="Y59" s="3" t="n">
+        <v>27.746311</v>
       </c>
       <c r="Z59" s="3" t="inlineStr">
         <is>
@@ -11679,10 +11675,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH59" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH59" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI59" s="3" t="inlineStr">
         <is>
@@ -11701,25 +11695,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN59" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN59" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
           <t>1,7</t>
         </is>
       </c>
-      <c r="AP59" s="3" t="inlineStr">
-        <is>
-          <t>85.408967</t>
-        </is>
+      <c r="AP59" s="3" t="n">
+        <v>85.408967</v>
       </c>
       <c r="AQ59" s="3" t="inlineStr"/>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
@@ -11815,10 +11805,8 @@
           <t>Sachin Magar</t>
         </is>
       </c>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
-          <t>9849737950</t>
-        </is>
+      <c r="O60" s="3" t="n">
+        <v>9849737950</v>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
@@ -11853,10 +11841,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y60" s="3" t="inlineStr">
-        <is>
-          <t>27.75371</t>
-        </is>
+      <c r="Y60" s="3" t="n">
+        <v>27.75371</v>
       </c>
       <c r="Z60" s="3" t="inlineStr">
         <is>
@@ -11912,25 +11898,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN60" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN60" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
           <t>3,9</t>
         </is>
       </c>
-      <c r="AP60" s="3" t="inlineStr">
-        <is>
-          <t>85.34744</t>
-        </is>
+      <c r="AP60" s="3" t="n">
+        <v>85.34744000000001</v>
       </c>
       <c r="AQ60" s="3" t="inlineStr"/>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
@@ -12026,10 +12008,8 @@
           <t>Sachin Magar</t>
         </is>
       </c>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
-          <t>9849737950</t>
-        </is>
+      <c r="O61" s="3" t="n">
+        <v>9849737950</v>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
@@ -12064,10 +12044,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y61" s="3" t="inlineStr">
-        <is>
-          <t>27.75371</t>
-        </is>
+      <c r="Y61" s="3" t="n">
+        <v>27.75371</v>
       </c>
       <c r="Z61" s="3" t="inlineStr">
         <is>
@@ -12123,25 +12101,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN61" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN61" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
           <t>3,9</t>
         </is>
       </c>
-      <c r="AP61" s="3" t="inlineStr">
-        <is>
-          <t>85.34744</t>
-        </is>
+      <c r="AP61" s="3" t="n">
+        <v>85.34744000000001</v>
       </c>
       <c r="AQ61" s="3" t="inlineStr"/>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
@@ -12237,10 +12211,8 @@
           <t>Salina Alemagar</t>
         </is>
       </c>
-      <c r="O62" s="3" t="inlineStr">
-        <is>
-          <t>9841347466</t>
-        </is>
+      <c r="O62" s="3" t="n">
+        <v>9841347466</v>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
@@ -12326,10 +12298,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN62" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN62" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
@@ -12340,32 +12310,438 @@
       <c r="AQ62" s="3" t="inlineStr"/>
       <c r="AR62" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS62" s="3" t="inlineStr">
+        <is>
+          <t>2h 34m</t>
+        </is>
+      </c>
+      <c r="AT62" s="3" t="inlineStr">
+        <is>
+          <t>2h 34m</t>
+        </is>
+      </c>
+      <c r="AU62" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV62" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS62" s="3" t="inlineStr">
-        <is>
-          <t>2h 34m</t>
-        </is>
-      </c>
-      <c r="AT62" s="3" t="inlineStr">
-        <is>
-          <t>2h 34m</t>
-        </is>
-      </c>
-      <c r="AU62" s="3" t="inlineStr">
+      <c r="AW62" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 3:35 PM</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>TKT1331550</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>Prem Devi Shah</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>Prem Devi Shah</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>9809792343</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr"/>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:35:36 PM</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr"/>
+      <c r="T63" s="3" t="inlineStr"/>
+      <c r="U63" s="3" t="inlineStr">
+        <is>
+          <t>9809792343</t>
+        </is>
+      </c>
+      <c r="V63" s="3" t="inlineStr">
+        <is>
+          <t>12 Sep 2026 05:12:50 PM</t>
+        </is>
+      </c>
+      <c r="W63" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:35:36 PM</t>
+        </is>
+      </c>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y63" s="3" t="inlineStr"/>
+      <c r="Z63" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA63" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB63" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC63" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD63" s="3" t="inlineStr"/>
+      <c r="AE63" s="3" t="inlineStr">
+        <is>
+          <t>Laxmi Furniture - Furniture rental service Shital Height 44700, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF63" s="3" t="inlineStr"/>
+      <c r="AG63" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH63" s="3" t="inlineStr"/>
+      <c r="AI63" s="3" t="inlineStr">
+        <is>
+          <t>04:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ63" s="3" t="inlineStr"/>
+      <c r="AK63" s="3" t="inlineStr"/>
+      <c r="AL63" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM63" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN63" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO63" s="3" t="inlineStr">
+        <is>
+          <t>L61-1</t>
+        </is>
+      </c>
+      <c r="AP63" s="3" t="inlineStr"/>
+      <c r="AQ63" s="3" t="inlineStr"/>
+      <c r="AR63" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS63" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT63" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 22m</t>
+        </is>
+      </c>
+      <c r="AU63" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV63" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW63" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 3:35 PM</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>slow internet</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334412</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>Kishwor Khanal</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>Kishwor Khanal</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>9843123637</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="inlineStr"/>
+      <c r="R64" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:22:53 PM</t>
+        </is>
+      </c>
+      <c r="S64" s="3" t="inlineStr"/>
+      <c r="T64" s="3" t="inlineStr"/>
+      <c r="U64" s="3" t="inlineStr">
+        <is>
+          <t>9843123637</t>
+        </is>
+      </c>
+      <c r="V64" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:00:05 PM</t>
+        </is>
+      </c>
+      <c r="W64" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:35:34 PM</t>
+        </is>
+      </c>
+      <c r="X64" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y64" s="3" t="inlineStr">
+        <is>
+          <t>27.705894</t>
+        </is>
+      </c>
+      <c r="Z64" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA64" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB64" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC64" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD64" s="3" t="inlineStr"/>
+      <c r="AE64" s="3" t="inlineStr">
+        <is>
+          <t>Purnima Press Details from Google Maps P844+M85, Sahid Nigurna Marg, Kathmandu 44600, Bagmati, Centr</t>
+        </is>
+      </c>
+      <c r="AF64" s="3" t="inlineStr"/>
+      <c r="AG64" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="AH64" s="3" t="inlineStr"/>
+      <c r="AI64" s="3" t="inlineStr">
+        <is>
+          <t>13:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ64" s="3" t="inlineStr"/>
+      <c r="AK64" s="3" t="inlineStr"/>
+      <c r="AL64" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM64" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN64" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO64" s="3" t="inlineStr">
+        <is>
+          <t>CDB288</t>
+        </is>
+      </c>
+      <c r="AP64" s="3" t="inlineStr">
+        <is>
+          <t>85.306163</t>
+        </is>
+      </c>
+      <c r="AQ64" s="3" t="inlineStr"/>
+      <c r="AR64" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS64" s="3" t="inlineStr">
+        <is>
+          <t>23h 12m</t>
+        </is>
+      </c>
+      <c r="AT64" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 35m</t>
+        </is>
+      </c>
+      <c r="AU64" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV62" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW62" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV64" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW64" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -12380,7 +12756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -12417,7 +12793,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
@@ -12427,7 +12803,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -12438,7 +12814,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>68.3%</t>
         </is>
       </c>
     </row>
@@ -12450,7 +12826,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7d 3h 3m</t>
+          <t>6d 19h 38m</t>
         </is>
       </c>
     </row>
@@ -12462,7 +12838,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>8d 9h 14m</t>
+          <t>8d 2h 43m</t>
         </is>
       </c>
     </row>
@@ -12503,14 +12879,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -12539,14 +12915,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -12647,14 +13023,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>81.6%</t>
         </is>
       </c>
     </row>
@@ -12808,14 +13184,14 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15889,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
@@ -15580,7 +15956,7 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -15647,7 +16023,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
@@ -15714,14 +16090,14 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
           <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
           <t>16 Sep 2026 12:51:50 PM</t>
@@ -15745,6 +16121,140 @@
       <c r="M75" s="5" t="inlineStr">
         <is>
           <t>2h 34m</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>TKT1331550</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Prem Devi Shah</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:35:36 PM</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>12 Sep 2026 05:12:50 PM</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:35:36 PM</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334412</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Kishwor Khanal</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:22:53 PM</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:00:05 PM</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:35:34 PM</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>23h 12m</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>1d 3h 35m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW64"/>
+  <dimension ref="A1:AW65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -12406,10 +12406,8 @@
           <t>Prem Devi Shah</t>
         </is>
       </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
-          <t>9809792343</t>
-        </is>
+      <c r="O63" s="3" t="n">
+        <v>9809792343</v>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
@@ -12495,10 +12493,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN63" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN63" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO63" s="3" t="inlineStr">
         <is>
@@ -12509,7 +12505,7 @@
       <c r="AQ63" s="3" t="inlineStr"/>
       <c r="AR63" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS63" s="3" t="inlineStr">
@@ -12605,10 +12601,8 @@
           <t>Kishwor Khanal</t>
         </is>
       </c>
-      <c r="O64" s="3" t="inlineStr">
-        <is>
-          <t>9843123637</t>
-        </is>
+      <c r="O64" s="3" t="n">
+        <v>9843123637</v>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
@@ -12643,10 +12637,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y64" s="3" t="inlineStr">
-        <is>
-          <t>27.705894</t>
-        </is>
+      <c r="Y64" s="3" t="n">
+        <v>27.705894</v>
       </c>
       <c r="Z64" s="3" t="inlineStr">
         <is>
@@ -12698,50 +12690,249 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN64" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN64" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
           <t>CDB288</t>
         </is>
       </c>
-      <c r="AP64" s="3" t="inlineStr">
-        <is>
-          <t>85.306163</t>
-        </is>
+      <c r="AP64" s="3" t="n">
+        <v>85.306163</v>
       </c>
       <c r="AQ64" s="3" t="inlineStr"/>
       <c r="AR64" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS64" s="3" t="inlineStr">
+        <is>
+          <t>23h 12m</t>
+        </is>
+      </c>
+      <c r="AT64" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 35m</t>
+        </is>
+      </c>
+      <c r="AU64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV64" s="3" t="inlineStr">
+        <is>
           <t>Case : slow internet  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS64" s="3" t="inlineStr">
-        <is>
-          <t>23h 12m</t>
-        </is>
-      </c>
-      <c r="AT64" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h 35m</t>
-        </is>
-      </c>
-      <c r="AU64" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV64" s="3" t="inlineStr">
-        <is>
-          <t>Case : slow internet  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW64" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 3:59 PM</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335704</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>R.G.S Trade concern Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>R.G.S Trade concern Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>9843047160</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr"/>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:59:36 PM</t>
+        </is>
+      </c>
+      <c r="S65" s="3" t="inlineStr"/>
+      <c r="T65" s="3" t="inlineStr"/>
+      <c r="U65" s="3" t="inlineStr">
+        <is>
+          <t>LTP9843047160</t>
+        </is>
+      </c>
+      <c r="V65" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:36:20 PM</t>
+        </is>
+      </c>
+      <c r="W65" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:59:36 PM</t>
+        </is>
+      </c>
+      <c r="X65" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y65" s="3" t="inlineStr"/>
+      <c r="Z65" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA65" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB65" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC65" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD65" s="3" t="inlineStr"/>
+      <c r="AE65" s="3" t="inlineStr">
+        <is>
+          <t>Intense Fitness - Best in imadole. - Fitness center F072 Mahalaxmi, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF65" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG65" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH65" s="3" t="inlineStr"/>
+      <c r="AI65" s="3" t="inlineStr">
+        <is>
+          <t>02:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ65" s="3" t="inlineStr"/>
+      <c r="AK65" s="3" t="inlineStr"/>
+      <c r="AL65" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM65" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN65" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO65" s="3" t="inlineStr">
+        <is>
+          <t>4,10</t>
+        </is>
+      </c>
+      <c r="AP65" s="3" t="inlineStr"/>
+      <c r="AQ65" s="3" t="inlineStr"/>
+      <c r="AR65" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS65" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT65" s="3" t="inlineStr">
+        <is>
+          <t>2h 23m</t>
+        </is>
+      </c>
+      <c r="AU65" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV65" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW65" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -12793,7 +12984,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -12803,7 +12994,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -12814,7 +13005,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -12826,7 +13017,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6d 19h 38m</t>
+          <t>6d 15h 55m</t>
         </is>
       </c>
     </row>
@@ -12838,7 +13029,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>8d 2h 43m</t>
+          <t>7d 22h 20m</t>
         </is>
       </c>
     </row>
@@ -12879,14 +13070,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>80.5%</t>
         </is>
       </c>
     </row>
@@ -13023,14 +13214,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>82.1%</t>
         </is>
       </c>
     </row>
@@ -16157,7 +16348,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
@@ -16224,14 +16415,14 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
           <t>Case : slow internet  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>Case : slow internet  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
           <t>15 Sep 2026 04:22:53 PM</t>
@@ -16255,6 +16446,73 @@
       <c r="M77" s="5" t="inlineStr">
         <is>
           <t>1d 3h 35m</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335704</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>R.G.S Trade concern Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:59:36 PM</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 01:36:20 PM</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:59:36 PM</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>2h 23m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW65"/>
+  <dimension ref="A1:AW66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -12800,10 +12800,8 @@
           <t>R.G.S Trade concern Pvt Ltd</t>
         </is>
       </c>
-      <c r="O65" s="3" t="inlineStr">
-        <is>
-          <t>9843047160</t>
-        </is>
+      <c r="O65" s="3" t="n">
+        <v>9843047160</v>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
@@ -12893,10 +12891,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN65" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN65" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO65" s="3" t="inlineStr">
         <is>
@@ -12907,32 +12903,243 @@
       <c r="AQ65" s="3" t="inlineStr"/>
       <c r="AR65" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS65" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT65" s="3" t="inlineStr">
+        <is>
+          <t>2h 23m</t>
+        </is>
+      </c>
+      <c r="AU65" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV65" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS65" s="3" t="inlineStr">
+      <c r="AW65" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 4:15 PM</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335504</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>Sakil Raj Bajracharya</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>Sakil Raj Bajracharya</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>9808397393</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q66" s="3" t="inlineStr"/>
+      <c r="R66" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 04:15:31 PM</t>
+        </is>
+      </c>
+      <c r="S66" s="3" t="inlineStr"/>
+      <c r="T66" s="3" t="inlineStr"/>
+      <c r="U66" s="3" t="inlineStr">
+        <is>
+          <t>9851099939</t>
+        </is>
+      </c>
+      <c r="V66" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:05:50 AM</t>
+        </is>
+      </c>
+      <c r="W66" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 04:15:31 PM</t>
+        </is>
+      </c>
+      <c r="X66" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y66" s="3" t="inlineStr">
+        <is>
+          <t>27.66769</t>
+        </is>
+      </c>
+      <c r="Z66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA66" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB66" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC66" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD66" s="3" t="inlineStr"/>
+      <c r="AE66" s="3" t="inlineStr">
+        <is>
+          <t>Global IME Bank,Lagankhel, front of Mental Hospital ,Lalitpur-19, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF66" s="3" t="inlineStr">
+        <is>
+          <t>raj_sakil@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG66" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH66" s="3" t="inlineStr"/>
+      <c r="AI66" s="3" t="inlineStr">
+        <is>
+          <t>05:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ66" s="3" t="inlineStr"/>
+      <c r="AK66" s="3" t="inlineStr"/>
+      <c r="AL66" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM66" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN66" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO66" s="3" t="inlineStr">
+        <is>
+          <t>2,1</t>
+        </is>
+      </c>
+      <c r="AP66" s="3" t="inlineStr">
+        <is>
+          <t>85.32237</t>
+        </is>
+      </c>
+      <c r="AQ66" s="3" t="inlineStr"/>
+      <c r="AR66" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS66" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT65" s="3" t="inlineStr">
-        <is>
-          <t>2h 23m</t>
-        </is>
-      </c>
-      <c r="AU65" s="3" t="inlineStr">
+      <c r="AT66" s="3" t="inlineStr">
+        <is>
+          <t>5h 9m</t>
+        </is>
+      </c>
+      <c r="AU66" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV65" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW65" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV66" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -12947,7 +13154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -12984,7 +13191,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -12994,7 +13201,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -13005,7 +13212,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -13017,7 +13224,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6d 15h 55m</t>
+          <t>6d 12h 22m</t>
         </is>
       </c>
     </row>
@@ -13029,7 +13236,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>7d 22h 20m</t>
+          <t>7d 18h 13m</t>
         </is>
       </c>
     </row>
@@ -13070,14 +13277,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>81.0%</t>
         </is>
       </c>
     </row>
@@ -13214,14 +13421,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>82.5%</t>
         </is>
       </c>
     </row>
@@ -16482,14 +16689,14 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
           <t>16 Sep 2026 03:59:36 PM</t>
@@ -16513,6 +16720,73 @@
       <c r="M78" s="3" t="inlineStr">
         <is>
           <t>2h 23m</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>TKT1335504</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Sakil Raj Bajracharya</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 04:15:31 PM</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 11:05:50 AM</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 04:15:31 PM</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M79" s="5" t="inlineStr">
+        <is>
+          <t>5h 9m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -12999,10 +12999,8 @@
           <t>Sakil Raj Bajracharya</t>
         </is>
       </c>
-      <c r="O66" s="3" t="inlineStr">
-        <is>
-          <t>9808397393</t>
-        </is>
+      <c r="O66" s="3" t="n">
+        <v>9808397393</v>
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
@@ -13037,10 +13035,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y66" s="3" t="inlineStr">
-        <is>
-          <t>27.66769</t>
-        </is>
+      <c r="Y66" s="3" t="n">
+        <v>27.66769</v>
       </c>
       <c r="Z66" s="3" t="inlineStr">
         <is>
@@ -13096,25 +13092,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN66" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN66" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO66" s="3" t="inlineStr">
         <is>
           <t>2,1</t>
         </is>
       </c>
-      <c r="AP66" s="3" t="inlineStr">
-        <is>
-          <t>85.32237</t>
-        </is>
+      <c r="AP66" s="3" t="n">
+        <v>85.32237000000001</v>
       </c>
       <c r="AQ66" s="3" t="inlineStr"/>
       <c r="AR66" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS66" s="3" t="inlineStr">
@@ -13163,7 +13155,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -16756,7 +16748,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW66"/>
+  <dimension ref="A1:AW67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -13135,6 +13135,217 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 4:56 PM</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>Case : single to dual  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>single to dual</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334694</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>Raj Kumar Thapa</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
+          <t>Raj Kumar Thapa</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>9851160619</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="inlineStr"/>
+      <c r="R67" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 04:56:51 PM</t>
+        </is>
+      </c>
+      <c r="S67" s="3" t="inlineStr"/>
+      <c r="T67" s="3" t="inlineStr"/>
+      <c r="U67" s="3" t="inlineStr">
+        <is>
+          <t>9851160619</t>
+        </is>
+      </c>
+      <c r="V67" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:45:17 PM</t>
+        </is>
+      </c>
+      <c r="W67" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 04:56:51 PM</t>
+        </is>
+      </c>
+      <c r="X67" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y67" s="3" t="inlineStr">
+        <is>
+          <t>27.71607</t>
+        </is>
+      </c>
+      <c r="Z67" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA67" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB67" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC67" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD67" s="3" t="inlineStr"/>
+      <c r="AE67" s="3" t="inlineStr">
+        <is>
+          <t>Sarbeshwor Mahadev Temple,Kathmandu , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF67" s="3" t="inlineStr">
+        <is>
+          <t>rkthapa99@yahoo.com</t>
+        </is>
+      </c>
+      <c r="AG67" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH67" s="3" t="inlineStr"/>
+      <c r="AI67" s="3" t="inlineStr">
+        <is>
+          <t>12:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ67" s="3" t="inlineStr"/>
+      <c r="AK67" s="3" t="inlineStr"/>
+      <c r="AL67" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM67" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN67" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO67" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP67" s="3" t="inlineStr">
+        <is>
+          <t>85.36851</t>
+        </is>
+      </c>
+      <c r="AQ67" s="3" t="inlineStr"/>
+      <c r="AR67" s="3" t="inlineStr">
+        <is>
+          <t>Case : single to dual  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS67" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT67" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 11m</t>
+        </is>
+      </c>
+      <c r="AU67" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV67" s="3" t="inlineStr">
+        <is>
+          <t>Case : single to dual  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW67" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13146,7 +13357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -13155,7 +13366,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -13183,7 +13394,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
@@ -13193,7 +13404,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -13204,7 +13415,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.7%</t>
         </is>
       </c>
     </row>
@@ -13216,7 +13427,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6d 12h 22m</t>
+          <t>6d 8h 58m</t>
         </is>
       </c>
     </row>
@@ -13228,7 +13439,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>7d 18h 13m</t>
+          <t>7d 14h 45m</t>
         </is>
       </c>
     </row>
@@ -13269,14 +13480,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>81.4%</t>
         </is>
       </c>
     </row>
@@ -13436,14 +13647,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -16782,6 +16993,73 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334694</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Raj Kumar Thapa</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>Case : single to dual  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>Case : single to dual  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 04:56:51 PM</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:45:17 PM</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 04:56:51 PM</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 11m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW67"/>
+  <dimension ref="A1:AW70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -13202,10 +13202,8 @@
           <t>Raj Kumar Thapa</t>
         </is>
       </c>
-      <c r="O67" s="3" t="inlineStr">
-        <is>
-          <t>9851160619</t>
-        </is>
+      <c r="O67" s="3" t="n">
+        <v>9851160619</v>
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
@@ -13240,10 +13238,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y67" s="3" t="inlineStr">
-        <is>
-          <t>27.71607</t>
-        </is>
+      <c r="Y67" s="3" t="n">
+        <v>27.71607</v>
       </c>
       <c r="Z67" s="3" t="inlineStr">
         <is>
@@ -13299,50 +13295,555 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN67" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN67" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO67" s="3" t="inlineStr">
         <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="AP67" s="3" t="inlineStr">
-        <is>
-          <t>85.36851</t>
-        </is>
+      <c r="AP67" s="3" t="n">
+        <v>85.36851</v>
       </c>
       <c r="AQ67" s="3" t="inlineStr"/>
       <c r="AR67" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS67" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT67" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 11m</t>
+        </is>
+      </c>
+      <c r="AU67" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV67" s="3" t="inlineStr">
+        <is>
           <t>Case : single to dual  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS67" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT67" s="3" t="inlineStr">
-        <is>
-          <t>1d 2h 11m</t>
-        </is>
-      </c>
-      <c r="AU67" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV67" s="3" t="inlineStr">
-        <is>
-          <t>Case : single to dual  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW67" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 5:25 PM</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>wifi6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335458</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>Y.R. Tyre Industries Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>Y.R. Tyre Industries Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>9762875249</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q68" s="3" t="inlineStr"/>
+      <c r="R68" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:41:04 AM</t>
+        </is>
+      </c>
+      <c r="S68" s="3" t="inlineStr"/>
+      <c r="T68" s="3" t="inlineStr"/>
+      <c r="U68" s="3" t="inlineStr">
+        <is>
+          <t>yrtyre_fttx</t>
+        </is>
+      </c>
+      <c r="V68" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:36:42 AM</t>
+        </is>
+      </c>
+      <c r="W68" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 05:25:16 PM</t>
+        </is>
+      </c>
+      <c r="X68" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y68" s="3" t="inlineStr"/>
+      <c r="Z68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA68" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB68" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC68" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD68" s="3" t="inlineStr"/>
+      <c r="AE68" s="3" t="inlineStr">
+        <is>
+          <t>lal darbar marg		, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF68" s="3" t="inlineStr">
+        <is>
+          <t>accounts@yrtyreindustries.com</t>
+        </is>
+      </c>
+      <c r="AG68" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH68" s="3" t="inlineStr"/>
+      <c r="AI68" s="3" t="inlineStr">
+        <is>
+          <t>06:48 hour</t>
+        </is>
+      </c>
+      <c r="AJ68" s="3" t="inlineStr"/>
+      <c r="AK68" s="3" t="inlineStr"/>
+      <c r="AL68" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM68" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN68" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO68" s="3" t="inlineStr">
+        <is>
+          <t>3,2</t>
+        </is>
+      </c>
+      <c r="AP68" s="3" t="inlineStr"/>
+      <c r="AQ68" s="3" t="inlineStr"/>
+      <c r="AR68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS68" s="3" t="inlineStr">
+        <is>
+          <t>6h 44m</t>
+        </is>
+      </c>
+      <c r="AT68" s="3" t="inlineStr">
+        <is>
+          <t>6h 48m</t>
+        </is>
+      </c>
+      <c r="AU68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW68" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 5:24 PM</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>wifi6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335458</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>Y.R. Tyre Industries Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>Y.R. Tyre Industries Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>9762875249</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr"/>
+      <c r="R69" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:41:04 AM</t>
+        </is>
+      </c>
+      <c r="S69" s="3" t="inlineStr"/>
+      <c r="T69" s="3" t="inlineStr"/>
+      <c r="U69" s="3" t="inlineStr">
+        <is>
+          <t>yrtyre_fttx</t>
+        </is>
+      </c>
+      <c r="V69" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:36:42 AM</t>
+        </is>
+      </c>
+      <c r="W69" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 05:25:16 PM</t>
+        </is>
+      </c>
+      <c r="X69" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y69" s="3" t="inlineStr"/>
+      <c r="Z69" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA69" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB69" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC69" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD69" s="3" t="inlineStr"/>
+      <c r="AE69" s="3" t="inlineStr">
+        <is>
+          <t>lal darbar marg		, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF69" s="3" t="inlineStr">
+        <is>
+          <t>accounts@yrtyreindustries.com</t>
+        </is>
+      </c>
+      <c r="AG69" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH69" s="3" t="inlineStr"/>
+      <c r="AI69" s="3" t="inlineStr">
+        <is>
+          <t>06:48 hour</t>
+        </is>
+      </c>
+      <c r="AJ69" s="3" t="inlineStr"/>
+      <c r="AK69" s="3" t="inlineStr"/>
+      <c r="AL69" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM69" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN69" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO69" s="3" t="inlineStr">
+        <is>
+          <t>3,2</t>
+        </is>
+      </c>
+      <c r="AP69" s="3" t="inlineStr"/>
+      <c r="AQ69" s="3" t="inlineStr"/>
+      <c r="AR69" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS69" s="3" t="inlineStr">
+        <is>
+          <t>6h 44m</t>
+        </is>
+      </c>
+      <c r="AT69" s="3" t="inlineStr">
+        <is>
+          <t>6h 48m</t>
+        </is>
+      </c>
+      <c r="AU69" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV69" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW69" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 5:31 PM</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr"/>
+      <c r="J70" s="3" t="inlineStr"/>
+      <c r="K70" s="3" t="inlineStr"/>
+      <c r="L70" s="3" t="inlineStr"/>
+      <c r="M70" s="3" t="inlineStr"/>
+      <c r="N70" s="3" t="inlineStr"/>
+      <c r="O70" s="3" t="inlineStr"/>
+      <c r="P70" s="3" t="inlineStr"/>
+      <c r="Q70" s="3" t="inlineStr"/>
+      <c r="R70" s="3" t="inlineStr"/>
+      <c r="S70" s="3" t="inlineStr"/>
+      <c r="T70" s="3" t="inlineStr"/>
+      <c r="U70" s="3" t="inlineStr"/>
+      <c r="V70" s="3" t="inlineStr"/>
+      <c r="W70" s="3" t="inlineStr"/>
+      <c r="X70" s="3" t="inlineStr"/>
+      <c r="Y70" s="3" t="inlineStr"/>
+      <c r="Z70" s="3" t="inlineStr"/>
+      <c r="AA70" s="3" t="inlineStr"/>
+      <c r="AB70" s="3" t="inlineStr"/>
+      <c r="AC70" s="3" t="inlineStr"/>
+      <c r="AD70" s="3" t="inlineStr"/>
+      <c r="AE70" s="3" t="inlineStr"/>
+      <c r="AF70" s="3" t="inlineStr"/>
+      <c r="AG70" s="3" t="inlineStr"/>
+      <c r="AH70" s="3" t="inlineStr"/>
+      <c r="AI70" s="3" t="inlineStr"/>
+      <c r="AJ70" s="3" t="inlineStr"/>
+      <c r="AK70" s="3" t="inlineStr"/>
+      <c r="AL70" s="3" t="inlineStr"/>
+      <c r="AM70" s="3" t="inlineStr"/>
+      <c r="AN70" s="3" t="inlineStr"/>
+      <c r="AO70" s="3" t="inlineStr"/>
+      <c r="AP70" s="3" t="inlineStr"/>
+      <c r="AQ70" s="3" t="inlineStr"/>
+      <c r="AR70" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS70" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT70" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU70" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV70" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW70" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -13394,7 +13895,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
@@ -13404,7 +13905,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -13415,7 +13916,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>69.6%</t>
         </is>
       </c>
     </row>
@@ -13427,7 +13928,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6d 8h 58m</t>
+          <t>6d 2h 52m</t>
         </is>
       </c>
     </row>
@@ -13439,7 +13940,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>7d 14h 45m</t>
+          <t>7d 7h 25m</t>
         </is>
       </c>
     </row>
@@ -13480,14 +13981,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>82.2%</t>
         </is>
       </c>
     </row>
@@ -13624,14 +14125,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -17026,14 +17527,14 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
           <t>Case : single to dual  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>Case : single to dual  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
           <t>16 Sep 2026 04:56:51 PM</t>
@@ -17057,6 +17558,140 @@
       <c r="M80" s="3" t="inlineStr">
         <is>
           <t>1d 2h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>TKT1335458</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Y.R. Tyre Industries Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:41:04 AM</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:36:42 AM</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 05:25:16 PM</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>6h 44m</t>
+        </is>
+      </c>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
+          <t>6h 48m</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335458</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Y.R. Tyre Industries Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:41:04 AM</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:36:42 AM</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 05:25:16 PM</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>6h 44m</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>6h 48m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW70"/>
+  <dimension ref="A1:AW71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -13405,10 +13405,8 @@
           <t>Y.R. Tyre Industries Pvt. Ltd</t>
         </is>
       </c>
-      <c r="O68" s="3" t="inlineStr">
-        <is>
-          <t>9762875249</t>
-        </is>
+      <c r="O68" s="3" t="n">
+        <v>9762875249</v>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
@@ -13498,10 +13496,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN68" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN68" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO68" s="3" t="inlineStr">
         <is>
@@ -13512,7 +13508,7 @@
       <c r="AQ68" s="3" t="inlineStr"/>
       <c r="AR68" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6 Router Upgrade  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS68" s="3" t="inlineStr">
@@ -13608,10 +13604,8 @@
           <t>Y.R. Tyre Industries Pvt. Ltd</t>
         </is>
       </c>
-      <c r="O69" s="3" t="inlineStr">
-        <is>
-          <t>9762875249</t>
-        </is>
+      <c r="O69" s="3" t="n">
+        <v>9762875249</v>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
@@ -13701,10 +13695,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN69" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN69" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO69" s="3" t="inlineStr">
         <is>
@@ -13715,7 +13707,7 @@
       <c r="AQ69" s="3" t="inlineStr"/>
       <c r="AR69" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6 Router Upgrade  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS69" s="3" t="inlineStr">
@@ -13847,6 +13839,217 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 5:33 PM</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334545</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>Hari Shrestha</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
+          <t>Hari Shrestha</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>9849932195</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="inlineStr"/>
+      <c r="R71" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 05:33:24 PM</t>
+        </is>
+      </c>
+      <c r="S71" s="3" t="inlineStr"/>
+      <c r="T71" s="3" t="inlineStr"/>
+      <c r="U71" s="3" t="inlineStr">
+        <is>
+          <t>9849932195</t>
+        </is>
+      </c>
+      <c r="V71" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:24:16 PM</t>
+        </is>
+      </c>
+      <c r="W71" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 05:33:58 PM</t>
+        </is>
+      </c>
+      <c r="X71" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y71" s="3" t="inlineStr">
+        <is>
+          <t>27.674608</t>
+        </is>
+      </c>
+      <c r="Z71" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA71" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB71" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC71" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD71" s="3" t="inlineStr"/>
+      <c r="AE71" s="3" t="inlineStr">
+        <is>
+          <t>Kirtipur ward no:9,Panga, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF71" s="3" t="inlineStr">
+        <is>
+          <t>hari.shrestha2049@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG71" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH71" s="3" t="inlineStr"/>
+      <c r="AI71" s="3" t="inlineStr">
+        <is>
+          <t>14:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ71" s="3" t="inlineStr"/>
+      <c r="AK71" s="3" t="inlineStr"/>
+      <c r="AL71" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM71" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN71" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO71" s="3" t="inlineStr">
+        <is>
+          <t>4,15</t>
+        </is>
+      </c>
+      <c r="AP71" s="3" t="inlineStr">
+        <is>
+          <t>85.279892</t>
+        </is>
+      </c>
+      <c r="AQ71" s="3" t="inlineStr"/>
+      <c r="AR71" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS71" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT71" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 9m</t>
+        </is>
+      </c>
+      <c r="AU71" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV71" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW71" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13858,7 +14061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -13895,7 +14098,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
@@ -13905,7 +14108,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
@@ -13916,7 +14119,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -13928,7 +14131,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6d 2h 52m</t>
+          <t>5d 23h 52m</t>
         </is>
       </c>
     </row>
@@ -13940,7 +14143,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>7d 7h 25m</t>
+          <t>7d 4h 24m</t>
         </is>
       </c>
     </row>
@@ -14053,10 +14256,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
@@ -14378,10 +14581,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
@@ -17594,7 +17797,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6 Router Upgrade  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -17661,14 +17864,14 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6 Router Upgrade  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6 Router Upgrade  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
           <t>16 Sep 2026 10:41:04 AM</t>
@@ -17692,6 +17895,73 @@
       <c r="M82" s="3" t="inlineStr">
         <is>
           <t>6h 48m</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334545</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Hari Shrestha</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 05:33:24 PM</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:24:16 PM</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 05:33:58 PM</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M83" s="5" t="inlineStr">
+        <is>
+          <t>1d 4h 9m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -13906,10 +13906,8 @@
           <t>Hari Shrestha</t>
         </is>
       </c>
-      <c r="O71" s="3" t="inlineStr">
-        <is>
-          <t>9849932195</t>
-        </is>
+      <c r="O71" s="3" t="n">
+        <v>9849932195</v>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
@@ -13944,10 +13942,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y71" s="3" t="inlineStr">
-        <is>
-          <t>27.674608</t>
-        </is>
+      <c r="Y71" s="3" t="n">
+        <v>27.674608</v>
       </c>
       <c r="Z71" s="3" t="inlineStr">
         <is>
@@ -14003,25 +13999,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN71" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN71" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO71" s="3" t="inlineStr">
         <is>
           <t>4,15</t>
         </is>
       </c>
-      <c r="AP71" s="3" t="inlineStr">
-        <is>
-          <t>85.279892</t>
-        </is>
+      <c r="AP71" s="3" t="n">
+        <v>85.279892</v>
       </c>
       <c r="AQ71" s="3" t="inlineStr"/>
       <c r="AR71" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS71" s="3" t="inlineStr">
@@ -14070,7 +14062,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -17931,7 +17923,7 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW71"/>
+  <dimension ref="A1:AW72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -14042,6 +14042,209 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 6:25 PM</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Case : limit exceed issue iptv  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>limit exceed issue iptv</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334961</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>Luna Joshi</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
+          <t>Luna Joshi</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>9841279425</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q72" s="3" t="inlineStr"/>
+      <c r="R72" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 06:25:14 PM</t>
+        </is>
+      </c>
+      <c r="S72" s="3" t="inlineStr"/>
+      <c r="T72" s="3" t="inlineStr"/>
+      <c r="U72" s="3" t="inlineStr">
+        <is>
+          <t>LTP9841279425</t>
+        </is>
+      </c>
+      <c r="V72" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:50:29 PM</t>
+        </is>
+      </c>
+      <c r="W72" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 06:25:14 PM</t>
+        </is>
+      </c>
+      <c r="X72" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y72" s="3" t="inlineStr"/>
+      <c r="Z72" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA72" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB72" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC72" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD72" s="3" t="inlineStr"/>
+      <c r="AE72" s="3" t="inlineStr">
+        <is>
+          <t>Innovative Engineering Services Pvt. Ltd. Details from Google Maps Lalitpur 44600, Lalitpur, Nepal,</t>
+        </is>
+      </c>
+      <c r="AF72" s="3" t="inlineStr">
+        <is>
+          <t>9841801815@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG72" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH72" s="3" t="inlineStr"/>
+      <c r="AI72" s="3" t="inlineStr">
+        <is>
+          <t>10:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ72" s="3" t="inlineStr"/>
+      <c r="AK72" s="3" t="inlineStr"/>
+      <c r="AL72" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM72" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN72" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO72" s="3" t="inlineStr">
+        <is>
+          <t>CDB063</t>
+        </is>
+      </c>
+      <c r="AP72" s="3" t="inlineStr"/>
+      <c r="AQ72" s="3" t="inlineStr"/>
+      <c r="AR72" s="3" t="inlineStr">
+        <is>
+          <t>Case : limit exceed issue iptv  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS72" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT72" s="3" t="inlineStr">
+        <is>
+          <t>1d 34m</t>
+        </is>
+      </c>
+      <c r="AU72" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV72" s="3" t="inlineStr">
+        <is>
+          <t>Case : limit exceed issue iptv  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW72" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14053,7 +14256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -14062,7 +14265,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -14090,7 +14293,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
@@ -14100,7 +14303,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
@@ -14111,7 +14314,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.4%</t>
         </is>
       </c>
     </row>
@@ -14123,7 +14326,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5d 23h 52m</t>
+          <t>5d 21h</t>
         </is>
       </c>
     </row>
@@ -14135,7 +14338,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>7d 4h 24m</t>
+          <t>7d 1h 27m</t>
         </is>
       </c>
     </row>
@@ -14212,14 +14415,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14657,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
@@ -14477,18 +14680,18 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -14500,41 +14703,41 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -14546,220 +14749,176 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr"/>
-      <c r="B31" s="5" t="inlineStr"/>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C31" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr"/>
+      <c r="B32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="5" t="n">
+      <c r="D32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>TKT1334942</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>INDIRA RANABHAT</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 08:35:54 AM</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 05:33:53 PM</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>16 Sep 2026 08:35:54 AM</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>15h 2m</t>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1334736</t>
+          <t>TKT1334942</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Dipendra Shrestha</t>
+          <t>INDIRA RANABHAT</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -14779,22 +14938,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:14:43 AM</t>
+          <t>16 Sep 2026 08:35:54 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:19:43 PM</t>
+          <t>15 Sep 2026 05:33:53 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:14:43 AM</t>
+          <t>16 Sep 2026 08:35:54 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -14804,29 +14963,29 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>17h 55m</t>
+          <t>15h 2m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1335101</t>
+          <t>TKT1334736</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Sudip Shrestha</t>
+          <t>Dipendra Shrestha</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14846,22 +15005,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:07:15 AM</t>
+          <t>16 Sep 2026 09:14:43 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:31:59 PM</t>
+          <t>15 Sep 2026 03:19:43 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:07:15 AM</t>
+          <t>16 Sep 2026 09:14:43 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -14871,29 +15030,29 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>12h 35m</t>
+          <t>17h 55m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1335000</t>
+          <t>TKT1335101</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Saman Shrestha</t>
+          <t>Sudip Shrestha</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -14913,22 +15072,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:44:13 AM</t>
+          <t>16 Sep 2026 09:07:15 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 06:47:39 PM</t>
+          <t>15 Sep 2026 08:31:59 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:44:13 AM</t>
+          <t>16 Sep 2026 09:07:15 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -14938,19 +15097,19 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>14h 56m</t>
+          <t>12h 35m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1334960</t>
+          <t>TKT1335000</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Raju Tamang</t>
+          <t>Saman Shrestha</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -14985,17 +15144,17 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:03:37 AM</t>
+          <t>16 Sep 2026 09:44:13 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:50:27 PM</t>
+          <t>15 Sep 2026 06:47:39 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:03:37 AM</t>
+          <t>16 Sep 2026 09:44:13 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -15005,19 +15164,19 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>16h 13m</t>
+          <t>14h 56m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1334610</t>
+          <t>TKT1334960</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>kran nepali</t>
+          <t>Raju Tamang</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -15027,7 +15186,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -15047,22 +15206,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:06:51 AM</t>
+          <t>16 Sep 2026 10:03:37 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:58:57 PM</t>
+          <t>15 Sep 2026 05:50:27 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:06:51 AM</t>
+          <t>16 Sep 2026 10:03:37 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -15072,19 +15231,19 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>20h 7m</t>
+          <t>16h 13m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1335114</t>
+          <t>TKT1334610</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Bishnu Bikram Khatri</t>
+          <t>kran nepali</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -15094,7 +15253,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -15114,22 +15273,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:18:36 AM</t>
+          <t>16 Sep 2026 10:06:51 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:43:35 PM</t>
+          <t>15 Sep 2026 01:58:57 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:18:36 AM</t>
+          <t>16 Sep 2026 10:06:51 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -15139,19 +15298,19 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>13h 35m</t>
+          <t>20h 7m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1191679</t>
+          <t>TKT1335114</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Gagan Kafle</t>
+          <t>Bishnu Bikram Khatri</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -15181,44 +15340,44 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Om Neupane</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>15 Jun 2026 03:38:40 PM</t>
+          <t>16 Sep 2026 10:18:36 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>24 May 2026 02:53:39 PM</t>
+          <t>15 Sep 2026 08:43:35 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:29:56 AM</t>
+          <t>16 Sep 2026 10:18:36 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>92d 18h 51m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>114d 19h 36m</t>
+          <t>13h 35m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1207844</t>
+          <t>TKT1191679</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Phursona Sherpa</t>
+          <t>Gagan Kafle</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -15248,54 +15407,54 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Om Neupane</t>
+          <t>Case :   has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>13 Jun 2026 01:15:04 PM</t>
+          <t>15 Jun 2026 03:38:40 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>06 Jun 2026 02:40:21 PM</t>
+          <t>24 May 2026 02:53:39 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:29:30 AM</t>
+          <t>16 Sep 2026 10:29:56 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>94d 21h 14m</t>
+          <t>92d 18h 51m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>101d 19h 49m</t>
+          <t>114d 19h 36m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1209820</t>
+          <t>TKT1207844</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Sanjib Thapa Magar</t>
+          <t>Phursona Sherpa</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -15315,54 +15474,54 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : Set up box not working   has been updated by Om Neupane</t>
+          <t>Case : wifi 6  has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>13 Jun 2026 01:46:51 PM</t>
+          <t>13 Jun 2026 01:15:04 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>07 Jun 2026 09:07:12 PM</t>
+          <t>06 Jun 2026 02:40:21 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:26:14 AM</t>
+          <t>16 Sep 2026 10:29:30 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>94d 20h 39m</t>
+          <t>94d 21h 14m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>100d 13h 19m</t>
+          <t>101d 19h 49m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1334895</t>
+          <t>TKT1209820</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>DITSA TECHNOLOGY PVT. LTD</t>
+          <t>Sanjib Thapa Magar</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -15382,44 +15541,44 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6 router  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Set up box not working   has been updated by Om Neupane</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:37:31 AM</t>
+          <t>13 Jun 2026 01:46:51 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:04:24 PM</t>
+          <t>07 Jun 2026 09:07:12 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:37:31 AM</t>
+          <t>16 Sep 2026 10:26:14 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>94d 20h 39m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>17h 33m</t>
+          <t>100d 13h 19m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1334982</t>
+          <t>TKT1334895</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Rinji Sherpa</t>
+          <t>DITSA TECHNOLOGY PVT. LTD</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -15449,22 +15608,22 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>Case : wifi6 router  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:35:51 AM</t>
+          <t>16 Sep 2026 10:37:31 AM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 06:26:14 PM</t>
+          <t>15 Sep 2026 05:04:24 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:35:51 AM</t>
+          <t>16 Sep 2026 10:37:31 AM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -15474,29 +15633,29 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>16h 9m</t>
+          <t>17h 33m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1334968</t>
+          <t>TKT1334982</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Pramod Pandey</t>
+          <t>Rinji Sherpa</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -15516,22 +15675,22 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:27:53 AM</t>
+          <t>16 Sep 2026 10:35:51 AM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 06:00:47 PM</t>
+          <t>15 Sep 2026 06:26:14 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:27:53 AM</t>
+          <t>16 Sep 2026 10:35:51 AM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -15541,7 +15700,7 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>16h 27m</t>
+          <t>16h 9m</t>
         </is>
       </c>
     </row>
@@ -15615,22 +15774,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1334824</t>
+          <t>TKT1334968</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Babu Ram Sunwar</t>
+          <t>Pramod Pandey</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15650,44 +15809,44 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>Case : 5  g   not shown   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:13:19 PM</t>
+          <t>16 Sep 2026 10:27:53 AM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:13:19 PM</t>
+          <t>15 Sep 2026 06:00:47 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:47:17 AM</t>
+          <t>16 Sep 2026 10:27:53 AM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>19h 33m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>19h 33m</t>
+          <t>16h 27m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1333669</t>
+          <t>TKT1334824</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Shankar Barahi</t>
+          <t>Babu Ram Sunwar</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -15717,44 +15876,44 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:41:03 AM</t>
+          <t>15 Sep 2026 04:13:19 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:35:12 PM</t>
+          <t>15 Sep 2026 04:13:19 PM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:41:03 AM</t>
+          <t>16 Sep 2026 11:47:17 AM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>19h 33m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1d 20h 5m</t>
+          <t>19h 33m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1332875</t>
+          <t>TKT1333669</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Prashansa Lamichhane</t>
+          <t>Shankar Barahi</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -15784,22 +15943,22 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+          <t>Case : WIFI 6 upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:55:37 AM</t>
+          <t>16 Sep 2026 11:41:03 AM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>13 Sep 2026 06:14:45 PM</t>
+          <t>14 Sep 2026 03:35:12 PM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:55:37 AM</t>
+          <t>16 Sep 2026 11:41:03 AM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -15809,19 +15968,19 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>2d 17h 40m</t>
+          <t>1d 20h 5m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1334603</t>
+          <t>TKT1332875</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Sudip Danai</t>
+          <t>Prashansa Lamichhane</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -15836,12 +15995,12 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -15851,54 +16010,54 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:56:11 PM</t>
+          <t>16 Sep 2026 11:55:37 AM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:56:11 PM</t>
+          <t>13 Sep 2026 06:14:45 PM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:50:53 AM</t>
+          <t>16 Sep 2026 11:55:37 AM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>21h 54m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>21h 54m</t>
+          <t>2d 17h 40m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1334891</t>
+          <t>TKT1334603</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Mohan krishna thapa</t>
+          <t>Sudip Danai</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -15918,54 +16077,54 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Ajit Shrestha</t>
+          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:50:32 PM</t>
+          <t>15 Sep 2026 01:56:11 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:02:14 PM</t>
+          <t>15 Sep 2026 01:56:11 PM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 12:29:34 PM</t>
+          <t>16 Sep 2026 11:50:53 AM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>15h 39m</t>
+          <t>21h 54m</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>19h 27m</t>
+          <t>21h 54m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1334862</t>
+          <t>TKT1334891</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Bishnu Dhakal</t>
+          <t>Mohan krishna thapa</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -15985,64 +16144,64 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router upgrade  has been updated by Sunil Chaudhary</t>
+          <t>Case : IPTV Issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:46:44 PM</t>
+          <t>15 Sep 2026 08:50:32 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:43:24 PM</t>
+          <t>15 Sep 2026 05:02:14 PM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 12:34:32 PM</t>
+          <t>16 Sep 2026 12:29:34 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>19h 47m</t>
+          <t>15h 39m</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>19h 51m</t>
+          <t>19h 27m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1334576</t>
+          <t>TKT1334862</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Gyan Prasad Gairi</t>
+          <t>Bishnu Dhakal</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -16052,32 +16211,32 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : Slow internet issue  has been updated by Rajesh Maharjan</t>
+          <t>Case : WIFI6 Router upgrade  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 12:47:02 PM</t>
+          <t>15 Sep 2026 04:46:44 PM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:43:29 PM</t>
+          <t>15 Sep 2026 04:43:24 PM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 12:47:02 PM</t>
+          <t>16 Sep 2026 12:34:32 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>19h 47m</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>23h 3m</t>
+          <t>19h 51m</t>
         </is>
       </c>
     </row>
@@ -16151,32 +16310,32 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1334854</t>
+          <t>TKT1334576</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Avinash Gyalzen Lama</t>
+          <t>Gyan Prasad Gairi</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -16186,44 +16345,44 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+          <t>Case : Slow internet issue  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:33:49 PM</t>
+          <t>16 Sep 2026 12:47:02 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:33:49 PM</t>
+          <t>15 Sep 2026 01:43:29 PM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:11:53 PM</t>
+          <t>16 Sep 2026 12:47:02 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>20h 38m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>20h 38m</t>
+          <t>23h 3m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1334938</t>
+          <t>TKT1334854</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Rajiv Bhandari</t>
+          <t>Avinash Gyalzen Lama</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -16238,12 +16397,12 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -16253,44 +16412,44 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:32:10 PM</t>
+          <t>15 Sep 2026 04:33:49 PM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:32:10 PM</t>
+          <t>15 Sep 2026 04:33:49 PM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:31:44 PM</t>
+          <t>16 Sep 2026 01:11:53 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>19h 59m</t>
+          <t>20h 38m</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>19h 59m</t>
+          <t>20h 38m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1335558</t>
+          <t>TKT1334938</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Roshan Rai</t>
+          <t>Rajiv Bhandari</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -16320,44 +16479,44 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:31:25 PM</t>
+          <t>15 Sep 2026 05:32:10 PM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:40:28 AM</t>
+          <t>15 Sep 2026 05:32:10 PM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:31:25 PM</t>
+          <t>16 Sep 2026 01:31:44 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>19h 59m</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>1h 50m</t>
+          <t>19h 59m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TKT1335471</t>
+          <t>TKT1335558</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Sarakha Human Search</t>
+          <t>Roshan Rai</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -16387,22 +16546,22 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:17:45 PM</t>
+          <t>16 Sep 2026 01:31:25 PM</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:45:16 AM</t>
+          <t>16 Sep 2026 11:40:28 AM</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:17:45 PM</t>
+          <t>16 Sep 2026 01:31:25 PM</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
@@ -16412,19 +16571,19 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>2h 32m</t>
+          <t>1h 50m</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>TKT1335555</t>
+          <t>TKT1335471</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Laxman Joshi</t>
+          <t>Sarakha Human Search</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -16454,22 +16613,22 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:36:54 PM</t>
+          <t>16 Sep 2026 01:17:45 PM</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:35:11 AM</t>
+          <t>16 Sep 2026 10:45:16 AM</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:36:54 PM</t>
+          <t>16 Sep 2026 01:17:45 PM</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
@@ -16479,19 +16638,19 @@
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>2h 1m</t>
+          <t>2h 32m</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TKT1334938</t>
+          <t>TKT1335555</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Rajiv Bhandari</t>
+          <t>Laxman Joshi</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -16506,12 +16665,12 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -16521,44 +16680,44 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:32:10 PM</t>
+          <t>16 Sep 2026 01:36:54 PM</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:32:10 PM</t>
+          <t>16 Sep 2026 11:35:11 AM</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:32:16 PM</t>
+          <t>16 Sep 2026 01:36:54 PM</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>2h 1m</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>TKT1334820</t>
+          <t>TKT1334938</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>nikhil bhattari</t>
+          <t>Rajiv Bhandari</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -16573,12 +16732,12 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -16588,44 +16747,44 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:41:26 PM</t>
+          <t>15 Sep 2026 05:32:10 PM</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:08:47 PM</t>
+          <t>15 Sep 2026 05:32:10 PM</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:41:26 PM</t>
+          <t>16 Sep 2026 01:32:16 PM</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>21h 32m</t>
+          <t>20h</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>TKT1334776</t>
+          <t>TKT1334820</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Sunita Lama</t>
+          <t>nikhil bhattari</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -16640,12 +16799,12 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -16655,44 +16814,44 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:44:39 PM</t>
+          <t>16 Sep 2026 01:41:26 PM</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:44:39 PM</t>
+          <t>15 Sep 2026 04:08:47 PM</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:50:42 PM</t>
+          <t>16 Sep 2026 01:41:26 PM</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>22h 6m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>22h 6m</t>
+          <t>21h 32m</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>TKT1335607</t>
+          <t>TKT1334776</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Gayatri Sharma</t>
+          <t>Sunita Lama</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -16707,12 +16866,12 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -16722,54 +16881,54 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 02:06:19 PM</t>
+          <t>15 Sep 2026 03:44:39 PM</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 12:12:31 PM</t>
+          <t>15 Sep 2026 03:44:39 PM</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 02:06:19 PM</t>
+          <t>16 Sep 2026 01:50:42 PM</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>22h 6m</t>
         </is>
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>1h 53m</t>
+          <t>22h 6m</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>TKT1335341</t>
+          <t>TKT1335607</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Roshan Dhimal</t>
+          <t>Gayatri Sharma</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -16789,22 +16948,22 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 02:23:14 PM</t>
+          <t>16 Sep 2026 02:06:19 PM</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 09:32:15 AM</t>
+          <t>16 Sep 2026 12:12:31 PM</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 02:23:14 PM</t>
+          <t>16 Sep 2026 02:06:19 PM</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
@@ -16814,29 +16973,29 @@
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>4h 50m</t>
+          <t>1h 53m</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>TKT1335539</t>
+          <t>TKT1335341</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Anigeet Nakarmi</t>
+          <t>Roshan Dhimal</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -16856,22 +17015,22 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : Router faulty  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 02:28:08 PM</t>
+          <t>16 Sep 2026 02:23:14 PM</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:23:39 AM</t>
+          <t>16 Sep 2026 09:32:15 AM</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 02:28:08 PM</t>
+          <t>16 Sep 2026 02:23:14 PM</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr">
@@ -16881,19 +17040,19 @@
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>3h 4m</t>
+          <t>4h 50m</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>TKT1334860</t>
+          <t>TKT1335539</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Sangita Rai</t>
+          <t>Anigeet Nakarmi</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -16908,12 +17067,12 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -16923,44 +17082,44 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:42:09 PM</t>
+          <t>16 Sep 2026 02:28:08 PM</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:42:09 PM</t>
+          <t>16 Sep 2026 11:23:39 AM</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 02:22:48 PM</t>
+          <t>16 Sep 2026 02:28:08 PM</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>21h 40m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>21h 40m</t>
+          <t>3h 4m</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>TKT1334908</t>
+          <t>TKT1334860</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Prajjwol Kandel</t>
+          <t>Sangita Rai</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -16990,32 +17149,32 @@
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:11:28 PM</t>
+          <t>15 Sep 2026 04:42:09 PM</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:11:28 PM</t>
+          <t>15 Sep 2026 04:42:09 PM</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 02:19:15 PM</t>
+          <t>16 Sep 2026 02:22:48 PM</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>21h 7m</t>
+          <t>21h 40m</t>
         </is>
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>21h 7m</t>
+          <t>21h 40m</t>
         </is>
       </c>
     </row>
@@ -17089,12 +17248,12 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>TKT1335478</t>
+          <t>TKT1334908</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Bikash Sakhya</t>
+          <t>Prajjwol Kandel</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -17109,12 +17268,12 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -17124,54 +17283,54 @@
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>Case : ROUTER UPGRADE  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 02:49:04 PM</t>
+          <t>15 Sep 2026 05:11:28 PM</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:50:07 AM</t>
+          <t>15 Sep 2026 05:11:28 PM</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 02:49:04 PM</t>
+          <t>16 Sep 2026 02:19:15 PM</t>
         </is>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>21h 7m</t>
         </is>
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>3h 58m</t>
+          <t>21h 7m</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>TKT1334489</t>
+          <t>TKT1335478</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Suvash Timilsina</t>
+          <t>Bikash Sakhya</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -17191,22 +17350,22 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sabin Giri</t>
+          <t>Case : ROUTER UPGRADE  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 03:27:24 PM</t>
+          <t>16 Sep 2026 02:49:04 PM</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:39:16 PM</t>
+          <t>16 Sep 2026 10:50:07 AM</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 03:27:24 PM</t>
+          <t>16 Sep 2026 02:49:04 PM</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
@@ -17216,29 +17375,29 @@
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>1d 2h 48m</t>
+          <t>3h 58m</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>TKT1335605</t>
+          <t>TKT1334489</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Sachin Magar</t>
+          <t>Suvash Timilsina</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17258,32 +17417,32 @@
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : iptv issue     has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 12:10:18 PM</t>
+          <t>16 Sep 2026 03:27:24 PM</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 12:10:18 PM</t>
+          <t>15 Sep 2026 12:39:16 PM</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 03:28:31 PM</t>
+          <t>16 Sep 2026 03:27:24 PM</t>
         </is>
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>3h 18m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>3h 18m</t>
+          <t>1d 2h 48m</t>
         </is>
       </c>
     </row>
@@ -17357,12 +17516,12 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>TKT1335663</t>
+          <t>TKT1335605</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Salina Alemagar</t>
+          <t>Sachin Magar</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -17377,12 +17536,12 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -17392,44 +17551,44 @@
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 12:51:50 PM</t>
+          <t>16 Sep 2026 12:10:18 PM</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 12:51:50 PM</t>
+          <t>16 Sep 2026 12:10:18 PM</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 03:26:43 PM</t>
+          <t>16 Sep 2026 03:28:31 PM</t>
         </is>
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>2h 34m</t>
+          <t>3h 18m</t>
         </is>
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>2h 34m</t>
+          <t>3h 18m</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>TKT1331550</t>
+          <t>TKT1335663</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Prem Devi Shah</t>
+          <t>Salina Alemagar</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -17444,12 +17603,12 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -17459,64 +17618,64 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 03:35:36 PM</t>
+          <t>16 Sep 2026 12:51:50 PM</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>12 Sep 2026 05:12:50 PM</t>
+          <t>16 Sep 2026 12:51:50 PM</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 03:35:36 PM</t>
+          <t>16 Sep 2026 03:26:43 PM</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2h 34m</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>3d 22h 22m</t>
+          <t>2h 34m</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>TKT1334412</t>
+          <t>TKT1331550</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Kishwor Khanal</t>
+          <t>Prem Devi Shah</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -17526,64 +17685,64 @@
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Ajit Shrestha</t>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:22:53 PM</t>
+          <t>16 Sep 2026 03:35:36 PM</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:00:05 PM</t>
+          <t>12 Sep 2026 05:12:50 PM</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 03:35:34 PM</t>
+          <t>16 Sep 2026 03:35:36 PM</t>
         </is>
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>23h 12m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>1d 3h 35m</t>
+          <t>3d 22h 22m</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>TKT1335704</t>
+          <t>TKT1334412</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>R.G.S Trade concern Pvt Ltd</t>
+          <t>Kishwor Khanal</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -17593,44 +17752,44 @@
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : slow internet  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 03:59:36 PM</t>
+          <t>15 Sep 2026 04:22:53 PM</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 01:36:20 PM</t>
+          <t>15 Sep 2026 12:00:05 PM</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 03:59:36 PM</t>
+          <t>16 Sep 2026 03:35:34 PM</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>23h 12m</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>2h 23m</t>
+          <t>1d 3h 35m</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>TKT1335504</t>
+          <t>TKT1335704</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Sakil Raj Bajracharya</t>
+          <t>R.G.S Trade concern Pvt Ltd</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -17660,22 +17819,22 @@
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 04:15:31 PM</t>
+          <t>16 Sep 2026 03:59:36 PM</t>
         </is>
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 11:05:50 AM</t>
+          <t>16 Sep 2026 01:36:20 PM</t>
         </is>
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 04:15:31 PM</t>
+          <t>16 Sep 2026 03:59:36 PM</t>
         </is>
       </c>
       <c r="L79" s="5" t="inlineStr">
@@ -17685,19 +17844,19 @@
       </c>
       <c r="M79" s="5" t="inlineStr">
         <is>
-          <t>5h 9m</t>
+          <t>2h 23m</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>TKT1334694</t>
+          <t>TKT1335504</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Raj Kumar Thapa</t>
+          <t>Sakil Raj Bajracharya</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -17707,7 +17866,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -17727,22 +17886,22 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>Case : single to dual  has been updated by Sabin Giri</t>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 04:56:51 PM</t>
+          <t>16 Sep 2026 04:15:31 PM</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:45:17 PM</t>
+          <t>16 Sep 2026 11:05:50 AM</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>16 Sep 2026 04:56:51 PM</t>
+          <t>16 Sep 2026 04:15:31 PM</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
@@ -17752,19 +17911,19 @@
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>1d 2h 11m</t>
+          <t>5h 9m</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>TKT1335458</t>
+          <t>TKT1334694</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Y.R. Tyre Industries Pvt. Ltd</t>
+          <t>Raj Kumar Thapa</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -17774,17 +17933,17 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -17794,32 +17953,32 @@
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6 Router Upgrade  has been updated by Ajit Shrestha</t>
+          <t>Case : single to dual  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:41:04 AM</t>
+          <t>16 Sep 2026 04:56:51 PM</t>
         </is>
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 10:36:42 AM</t>
+          <t>15 Sep 2026 02:45:17 PM</t>
         </is>
       </c>
       <c r="K81" s="5" t="inlineStr">
         <is>
-          <t>16 Sep 2026 05:25:16 PM</t>
+          <t>16 Sep 2026 04:56:51 PM</t>
         </is>
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>6h 44m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M81" s="5" t="inlineStr">
         <is>
-          <t>6h 48m</t>
+          <t>1d 2h 11m</t>
         </is>
       </c>
     </row>
@@ -17893,67 +18052,201 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
+          <t>TKT1335458</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Y.R. Tyre Industries Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6 Router Upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:41:04 AM</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 10:36:42 AM</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 05:25:16 PM</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>6h 44m</t>
+        </is>
+      </c>
+      <c r="M83" s="5" t="inlineStr">
+        <is>
+          <t>6h 48m</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
           <t>TKT1334545</t>
         </is>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>Hari Shrestha</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>Slow Internet Connection</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="E84" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr">
+      <c r="F84" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G83" s="5" t="inlineStr">
+      <c r="G84" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr">
+      <c r="H84" s="3" t="inlineStr">
         <is>
           <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr">
+      <c r="I84" s="3" t="inlineStr">
         <is>
           <t>16 Sep 2026 05:33:24 PM</t>
         </is>
       </c>
-      <c r="J83" s="5" t="inlineStr">
+      <c r="J84" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 01:24:16 PM</t>
         </is>
       </c>
-      <c r="K83" s="5" t="inlineStr">
+      <c r="K84" s="3" t="inlineStr">
         <is>
           <t>16 Sep 2026 05:33:58 PM</t>
         </is>
       </c>
-      <c r="L83" s="5" t="inlineStr">
+      <c r="L84" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M83" s="5" t="inlineStr">
+      <c r="M84" s="3" t="inlineStr">
         <is>
           <t>1d 4h 9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334961</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Luna Joshi</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>Case : limit exceed issue iptv  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>Case : limit exceed issue iptv  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 06:25:14 PM</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:50:29 PM</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 06:25:14 PM</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M85" s="5" t="inlineStr">
+        <is>
+          <t>1d 34m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_16_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_16_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -14109,10 +14109,8 @@
           <t>Luna Joshi</t>
         </is>
       </c>
-      <c r="O72" s="3" t="inlineStr">
-        <is>
-          <t>9841279425</t>
-        </is>
+      <c r="O72" s="3" t="n">
+        <v>9841279425</v>
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
@@ -14202,10 +14200,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN72" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN72" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO72" s="3" t="inlineStr">
         <is>
@@ -14216,7 +14212,7 @@
       <c r="AQ72" s="3" t="inlineStr"/>
       <c r="AR72" s="3" t="inlineStr">
         <is>
-          <t>Case : limit exceed issue iptv  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS72" s="3" t="inlineStr">
@@ -14265,7 +14261,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -18216,7 +18212,7 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Case : limit exceed issue iptv  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
